--- a/context_DB/SYR_context_db.xlsx
+++ b/context_DB/SYR_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ21"/>
+  <dimension ref="A1:AQ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,158 +648,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SY0200</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2024-11-29 ---- 2024-11-29 ---- 2024-11-09 ---- 2024-11-09 ---- 2024-10-23 ---- 2024-01-01</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>November 2024: A school was hit by Syrian and Russian airstrikes. ---- November 2024: A school was hit by Syrian and Russian airstrikes. ---- November 2024: A school was hit by shelling by Syrian forces.  ---- November 2024: A school was hit by shelling by Syrian forces.  ---- October 2024: The vicinity of an educational facility was hit by heavy artillery fired by Syrian regime forces. ---- January 2024: Syrian regime forces fired shells and rockets which struck a school and nearby buildings, causing varying degrees of destruction. Three civilians killed and four injured, including a baby.</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Other ---- Other ---- Other ---- Other ---- Other ---- Other</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Syrian or Russian Forces ---- Syrian or Russian Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Aerial Bomb: Plane ---- Aerial Bomb: Plane ---- Shelling ---- Shelling ---- Artillery ---- Rocket</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>School: No Further Details ---- School: No Further Details ---- Secondary School ---- Secondary School ---- School: No Further Details ---- School: No Further Details</t>
-        </is>
-      </c>
+          <t>SY0100</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Aleppo</t>
+          <t>Damascus</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>SY02</t>
+          <t>SY01</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence ---- Protests ---- Violence against civilians ---- Violence against civilians ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Battles ---- Explosions/Remote violence ---- Battles ---- Riots ---- Protests ---- Violence against civilians ---- Protests ---- Violence against civilians ---- Protests ---- Violence against civilians ---- Protests ---- Protests ---- Riots</t>
+          <t>Explosions/Remote violence ---- Strategic developments ---- Protests ---- Protests ---- Riots ---- Strategic developments ---- Strategic developments</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Shelling/artillery/missile attack ---- Peaceful protest ---- Abduction/forced disappearance ---- Attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Air/drone strike ---- Air/drone strike ---- Non-state actor overtakes territory ---- Air/drone strike ---- Non-state actor overtakes territory ---- Mob violence ---- Peaceful protest ---- Abduction/forced disappearance ---- Peaceful protest ---- Attack ---- Peaceful protest ---- Attack ---- Peaceful protest ---- Peaceful protest ---- Mob violence</t>
+          <t>Air/drone strike ---- Other ---- Peaceful protest ---- Peaceful protest ---- Mob violence ---- Arrests ---- Arrests</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Military Forces of Syria (2000-2024) ---- Protesters (Syria) ---- PKK: Kurdistan Workers Party ---- PKK: Kurdistan Workers Party ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Russia (2000-) ---- Military Forces of Syria (2000-2024) ---- Military Operations Command ---- Military Forces of Syria (2000-2024) ---- JWS: Syrian National Army ---- Rioters (Syria) ---- Protesters (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Rioters (Syria)</t>
+          <t>Military Forces of Israel (2022-) ---- Military Forces of Syria (2000-2024) Prison Guards ---- Protesters (Syria) ---- Protesters (Syria) ---- Rioters (Syria) ---- Police Forces of Syria (2024-) ---- Police Forces of Syria (2024-)</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Students (Syria) ---- YDG-H: Patriotic Revolutionary Youth Movement ---- YDG-H: Patriotic Revolutionary Youth Movement ---- Military Forces of Syria (2000-2024) ---- Military Forces of Russia (2000-) ---- Military Forces of Russia (2000-) ---- Students (Syria) ---- Students (Syria) ---- Students (Syria) ---- Students (Syria) ---- Teachers (Syria) ---- Students (Syria) ---- Students (Syria)</t>
+          <t>Students (Syria) ---- Students (Syria) ---- Students (Syria)</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2024-) General Security Forces ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+          <t>Military Forces of Iran (1989-) Islamic Revolutionary Guard Corps ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Students (Syria) ---- Students (Syria); Women (Syria) ---- Students (Syria); Teachers (Syria) ---- Students (Syria); Teachers (Syria) ---- YPG: Peoples Protection Units ---- Students (Syria); Women (Syria) ---- Teachers (Syria) ---- Alawite Muslim Group (Syria); Teachers (Syria) ---- Druze Group (Syria); Students (Syria)</t>
+          <t>Civilians (Syria) ---- Farmers (Syria); Prisoners (Syria); Teachers (Syria) ---- Druze Group (Syria); Students (Syria) ---- Kurdish Ethnic Group (Syria); Students (Syria) ---- Former Government of Syria (2024-)</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>On 10 March 2024, Syrian regime forces targeted a car with a guided missile in the vicinity of Daret Azza in the countryside of Aleppo, killing one child and wounding three civilians, including two children. The victims were students. 1 fatality. ---- On 20 March 2024, tens of students organized a protest in Kafr Karmin town in Aleppo countryside, in commemoration of the Syrian Revolution and to reiterate their support for the Syrian Revolution as it enters its thirteenth year. ---- On 27 April 2024, PKK's YDG-H (Al Shabiba Al Thawria) members detained a sixteen-year-old girl while she was returning from school in the city of Aleppo - Al-Ashrafiyya neighborhood for conscription. The victim's whereabouts remain unknown. ---- On 7 September 2024, PKK-affiliated Patriotic Revolutionary Youth Movement attacked a ceremony for high school students in Aleppo - Sheikh Maqsoud neighbourhood in the city of Aleppo and physically assaulted a number of the attendees, wounding some of them. ---- On 23 October 2024, regime forces shelled the vicinity of Al Zira'a school in western Aleppo countryside coded to Atareb district with heavy artillery. Casualties unknown. ---- On 29 October 2024, Syrian regime forces shelled the town of Daret Azza in the countryside of Aleppo with rockets and artillery, targeting a school and causing only material damage to the building. There were no casualties. ---- On 9 November 2024, regime fighters shelled schools, residential neighborhoods and agricultural land in Atareb and its outskirts in rural Aleppo with artillery and rockets, causing a fire in a residential home without causing any casualties. ---- On 28 November 2024, Russian and regime warplanes conducted airstrikes targeting the vicinity of an orphanage school in Atareb town in Aleppo countryside, killing 15 civilians including four children and two women, injuring five others including two children and causing material damage. 15 fatalities. ---- On 29 November 2024, Syrian and Russian warplanes conducted airstrikes targeting two schools in the town of Atareb in the countryside of Aleppo. There were no casualties. ---- On 29 November 2024, Military Operations Command forces advanced into the city of Aleppo as part of the 'Deter of Aggression/ 'Rad' Al 'dwan' operation and took control of Aleppo - University of Aleppo neighborhood following clashes with the Syrian regime forces. On the same day, artillery shelling targeted student housing at the university, killing four students and wounding others. Syrian regime forces and the Military Operations Command exchanged accusations regarding responsibility for the incident. 4 fatalities. ---- On 1 December 2024, Syrian and Russian warplanes conducted airstrikes targeting a monastery complex including a church, college and school in the city Aleppo - Al-Furqan neighborhood, causing material damage to church facilities and buildings without causing any casualties. ---- On 2 December 2024, JWS took control of the Military Infantry School north of Aleppo city following clashes with regime forces and YPG as part of operation 'Dawn of Freedom'. Casualties unknown. ---- On 5 January 2025, large-scale fist fight took place between students from two different governorates in the university dormitory in the Aleppo - University of Aleppo neighborhood in Aleppo city for unspecified reasons, leading General Security Forces to fire ammunition in the air to disperse the clashes, injuring several participants. There were no fatalities. ---- On 25 February 2025, residents held a protest in the city of Aleppo - Saadallah Al-Jabiri Square neighborhood in solidarity with ongoing protests in southern Syria condemning recent Israeli statement calling for the disarmament of southern Syria and condemning projects that threaten Syria's unity. On the same day, students from Dara province held a protest in the University of Aleppo condemning recent Israeli statements calling for the disarmament of southern Syria. ---- On 26 March 2025, unknown gunmen kidnapped a female student from Al-Ashrafiyya residents while she was heading to an educational institute in the Aleppo - Syriac Quarter neighborhood in Aleppo city. ---- On 8 April 2025, residents including students held a protest in the city of Aleppo - University of Aleppo supporting the Palestinian people and Dara residents recently killed by Israeli bombing, condemning Israeli attacks on Syrian territory and Israel's occupation of the Gaza strip. ---- On 28 April 2025, an unidentified armed group shot and killed a university professor in the city of Aleppo on allegations of affiliation with the ousted regime. 1 fatality. ---- On 18 May 2025, students staged a protest at Aleppo - University of Aleppo in the city of Aleppo, commemorating the first protest at the university that took place in May 2012. ---- On 1 June 2025, an unidentified armed group shot and killed a university professor from the Alawite sect in the city of Aleppo. The victim was the former dean of the Faculty of Civil Engineering at the University of Aleppo and is accused of collaborating with the Assad regime. 1 fatality. ---- On 6 July 2025, teachers staged a protest in the town of Atareb in the countryside of Aleppo, opposing the Minister of Education and the policies he is implementing. ---- On 17 July 2025, students from Aleppo University organized a protest at Aleppo - University of Aleppo in Aleppo city to condemn the crimes committed by the militias of Hikmat al-Hijri against Bedouin tribes in As-Sweida. ---- On 17 July 2025, student rioters attacked Druze students at the University of Aleppo in Aleppo - University of Aleppo neighborhood in Aleppo city amid rising tensions and following recent attacks on Bedouin tribes in As Sweida. Later, the president of the university addressed the students, calling for an end to the violence and urging them to calm the situation.</t>
+          <t>On 21 February 2024, Israeli warplanes carried out airstrikes targeting IRGC militias and hitting a building near the Iranian school in Kafr Sousah neighborhood in Damascus - Kafr Sousah city, killing two IRGC leaders and a civilian, as well as injuring others. The civilian victim was a fifty-two-year-old driver from Daraya city who was delivering an order to the Iranian school. 3 fatalities. ---- Mass grave: On 12 December 2024, locals found twelve bodies of former prisoners (teachers, farmers, drivers) who had died under torture in one of former regime prisons in a masss grave in the area between the fifth bridge and Happy Land in Damascus city. ---- On 2 February 2025, dozens of students staged a protest at Damascus - Umayyad Square in Damascus city, demanding the dismissal of the university president and a number of officials, accusing them of corruption and nepotism. ---- On 5 February 2025, students in the faculty of media and communications staged a protest in Damascus University in Damascus city, demanding the dismissal of professors linked to the former regime. ---- On 28 April 2025, students at the dormitory of Damascus University in Damascus city physically assaulted a number of students from As-Sweida province, amid sectarian chants. The incident occurred after a voice recording circulated among locals, allegedly featuring a Druze military commander from As-Sweida cursing the Prophet, which sparked widespread outrage. Police forces intervened to disperse the students and restore order. ---- On 26 June 2025, Syrian police members arrested nine young Kurdish men in the Shaalan area in Damascus city for unknown reasons. Four of the victims are from Quamishli city including three who were in the capital on a business trip and one who is a university student. ---- On 7 July 2025, Syrian police forces arrested the former Minister of Education under the Assad regime in the city of Damascus on charges of corruption.</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2024-03-10 ---- 2024-03-20 ---- 2024-04-27 ---- 2024-09-07 ---- 2024-10-23 ---- 2024-10-29 ---- 2024-11-09 ---- 2024-11-28 ---- 2024-11-29 ---- 2024-11-29 ---- 2024-12-01 ---- 2024-12-02 ---- 2025-01-05 ---- 2025-02-25 ---- 2025-03-26 ---- 2025-04-08 ---- 2025-04-28 ---- 2025-05-18 ---- 2025-06-01 ---- 2025-07-06 ---- 2025-07-17 ---- 2025-07-17</t>
+          <t>2024-02-21 ---- 2024-12-12 ---- 2025-02-02 ---- 2025-02-05 ---- 2025-04-28 ---- 2025-06-26 ---- 2025-07-07</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Jebel Saman</t>
+          <t>Damascus</t>
         </is>
       </c>
       <c r="AQ2" t="n">
@@ -809,11 +747,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SY0203</t>
+          <t>SY0200</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -828,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -840,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -861,48 +799,44 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-11-29 ---- 2024-11-29 ---- 2024-11-09 ---- 2024-11-09 ---- 2024-10-23 ---- 2024-01-01</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>October 2024: An educator was arrested at their home by the Syrian National Army (SNA) on accusations that they were working with the SDF.</t>
+          <t>November 2024: A school was hit by Syrian and Russian airstrikes. ---- November 2024: A school was hit by Syrian and Russian airstrikes. ---- November 2024: A school was hit by shelling by Syrian forces.  ---- November 2024: A school was hit by shelling by Syrian forces.  ---- October 2024: The vicinity of an educational facility was hit by heavy artillery fired by Syrian regime forces. ---- January 2024: Syrian regime forces fired shells and rockets which struck a school and nearby buildings, causing varying degrees of destruction. Three civilians killed and four injured, including a baby.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Other ---- Other ---- Other ---- Other ---- Other ---- Other</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Syrian National Army (SNA)</t>
+          <t>Syrian or Russian Forces ---- Syrian or Russian Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>No Information on the Weapon Used</t>
+          <t>Aerial Bomb: Plane ---- Aerial Bomb: Plane ---- Shelling ---- Shelling ---- Artillery ---- Rocket</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>NoInformation</t>
-        </is>
-      </c>
+          <t>School: No Further Details ---- School: No Further Details ---- Secondary School ---- Secondary School ---- School: No Further Details ---- School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
@@ -911,10 +845,10 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -924,47 +858,47 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Protests ---- Violence against civilians ---- Protests</t>
+          <t>Explosions/Remote violence ---- Protests ---- Violence against civilians ---- Violence against civilians ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Battles ---- Explosions/Remote violence ---- Battles ---- Riots ---- Protests ---- Violence against civilians ---- Protests ---- Violence against civilians ---- Protests ---- Violence against civilians ---- Protests ---- Protests ---- Riots</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance ---- Peaceful protest ---- Abduction/forced disappearance ---- Peaceful protest</t>
+          <t>Shelling/artillery/missile attack ---- Peaceful protest ---- Abduction/forced disappearance ---- Attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Air/drone strike ---- Air/drone strike ---- Non-state actor overtakes territory ---- Air/drone strike ---- Non-state actor overtakes territory ---- Mob violence ---- Peaceful protest ---- Abduction/forced disappearance ---- Peaceful protest ---- Attack ---- Peaceful protest ---- Attack ---- Peaceful protest ---- Peaceful protest ---- Mob violence</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>National Police Forces ---- Protesters (Syria) ---- National Police Forces ---- Protesters (Syria)</t>
+          <t>Military Forces of Syria (2000-2024) ---- Protesters (Syria) ---- PKK: Kurdistan Workers Party ---- PKK: Kurdistan Workers Party ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Russia (2000-) ---- Military Forces of Syria (2000-2024) ---- Military Operations Command ---- Military Forces of Syria (2000-2024) ---- JWS: Syrian National Army ---- Rioters (Syria) ---- Protesters (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Rioters (Syria)</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Students (Syria) ---- Students (Syria)</t>
+          <t>Students (Syria) ---- YDG-H: Patriotic Revolutionary Youth Movement ---- YDG-H: Patriotic Revolutionary Youth Movement ---- Military Forces of Syria (2000-2024) ---- Military Forces of Russia (2000-) ---- Military Forces of Russia (2000-) ---- Students (Syria) ---- Students (Syria) ---- Students (Syria) ---- Students (Syria) ---- Teachers (Syria) ---- Students (Syria) ---- Students (Syria)</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Civilians (Syria) ---- Civilians (Syria)</t>
+          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2024-) General Security Forces ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Teachers (Syria) ---- Teachers (Syria)</t>
+          <t>Students (Syria) ---- Students (Syria); Women (Syria) ---- Students (Syria); Teachers (Syria) ---- Students (Syria); Teachers (Syria) ---- YPG: Peoples Protection Units ---- Students (Syria); Women (Syria) ---- Teachers (Syria) ---- Alawite Muslim Group (Syria); Teachers (Syria) ---- Druze Group (Syria); Students (Syria)</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Around 27 January 2024 (week of), National Police Forces detained a forty-seven-year-old teacher who is from Turandah village in rural Aleppo for ransom after an IDP filed a complaint against the teacher over the sale of a newspaper business. The victims' whereabouts remain unknown. ---- On 11 September 2024, dozens of locals including students staged a protest in Afrin town in Aleppo countryside, and demanded a National Police Forces officer to be referred for investigation, after he stormed Omar Bin Al Khattab school in the town, arrested the school principal, and assaulted the teaching staff for not giving books to his son. ---- On 10 October 2024, National police forces detained a teacher in the village of Kafr Safra in the countryside of Jandairis (Afrin, Aleppo) on allegations of espionage for the QSD. ---- On 24 May 2025, students and their families staged a protest in the city of Afrin in the countryside of Aleppo for the second consecutive day, in rejection of the recent decision issued by the Ministry of Education to designate Aleppo as the sole center for conducting exams.</t>
+          <t>On 10 March 2024, Syrian regime forces targeted a car with a guided missile in the vicinity of Daret Azza in the countryside of Aleppo, killing one child and wounding three civilians, including two children. The victims were students. 1 fatality. ---- On 20 March 2024, tens of students organized a protest in Kafr Karmin town in Aleppo countryside, in commemoration of the Syrian Revolution and to reiterate their support for the Syrian Revolution as it enters its thirteenth year. ---- On 27 April 2024, PKK's YDG-H (Al Shabiba Al Thawria) members detained a sixteen-year-old girl while she was returning from school in the city of Aleppo - Al-Ashrafiyya neighborhood for conscription. The victim's whereabouts remain unknown. ---- On 7 September 2024, PKK-affiliated Patriotic Revolutionary Youth Movement attacked a ceremony for high school students in Aleppo - Sheikh Maqsoud neighbourhood in the city of Aleppo and physically assaulted a number of the attendees, wounding some of them. ---- On 23 October 2024, regime forces shelled the vicinity of Al Zira'a school in western Aleppo countryside coded to Atareb district with heavy artillery. Casualties unknown. ---- On 29 October 2024, Syrian regime forces shelled the town of Daret Azza in the countryside of Aleppo with rockets and artillery, targeting a school and causing only material damage to the building. There were no casualties. ---- On 9 November 2024, regime fighters shelled schools, residential neighborhoods and agricultural land in Atareb and its outskirts in rural Aleppo with artillery and rockets, causing a fire in a residential home without causing any casualties. ---- On 28 November 2024, Russian and regime warplanes conducted airstrikes targeting the vicinity of an orphanage school in Atareb town in Aleppo countryside, killing 15 civilians including four children and two women, injuring five others including two children and causing material damage. 15 fatalities. ---- On 29 November 2024, Syrian and Russian warplanes conducted airstrikes targeting two schools in the town of Atareb in the countryside of Aleppo. There were no casualties. ---- On 29 November 2024, Military Operations Command forces advanced into the city of Aleppo as part of the 'Deter of Aggression/ 'Rad' Al 'dwan' operation and took control of Aleppo - University of Aleppo neighborhood following clashes with the Syrian regime forces. On the same day, artillery shelling targeted student housing at the university, killing four students and wounding others. Syrian regime forces and the Military Operations Command exchanged accusations regarding responsibility for the incident. 4 fatalities. ---- On 1 December 2024, Syrian and Russian warplanes conducted airstrikes targeting a monastery complex including a church, college and school in the city Aleppo - Al-Furqan neighborhood, causing material damage to church facilities and buildings without causing any casualties. ---- On 2 December 2024, JWS took control of the Military Infantry School north of Aleppo city following clashes with regime forces and YPG as part of operation 'Dawn of Freedom'. Casualties unknown. ---- On 5 January 2025, large-scale fist fight took place between students from two different governorates in the university dormitory in the Aleppo - University of Aleppo neighborhood in Aleppo city for unspecified reasons, leading General Security Forces to fire ammunition in the air to disperse the clashes, injuring several participants. There were no fatalities. ---- On 25 February 2025, residents held a protest in the city of Aleppo - Saadallah Al-Jabiri Square neighborhood in solidarity with ongoing protests in southern Syria condemning recent Israeli statement calling for the disarmament of southern Syria and condemning projects that threaten Syria's unity. On the same day, students from Dara province held a protest in the University of Aleppo condemning recent Israeli statements calling for the disarmament of southern Syria. ---- On 26 March 2025, unknown gunmen kidnapped a female student from Al-Ashrafiyya residents while she was heading to an educational institute in the Aleppo - Syriac Quarter neighborhood in Aleppo city. ---- On 8 April 2025, residents including students held a protest in the city of Aleppo - University of Aleppo supporting the Palestinian people and Dara residents recently killed by Israeli bombing, condemning Israeli attacks on Syrian territory and Israel's occupation of the Gaza strip. ---- On 28 April 2025, an unidentified armed group shot and killed a university professor in the city of Aleppo on allegations of affiliation with the ousted regime. 1 fatality. ---- On 18 May 2025, students staged a protest at Aleppo - University of Aleppo in the city of Aleppo, commemorating the first protest at the university that took place in May 2012. ---- On 1 June 2025, an unidentified armed group shot and killed a university professor from the Alawite sect in the city of Aleppo. The victim was the former dean of the Faculty of Civil Engineering at the University of Aleppo and is accused of collaborating with the Assad regime. 1 fatality. ---- On 6 July 2025, teachers staged a protest in the town of Atareb in the countryside of Aleppo, opposing the Minister of Education and the policies he is implementing. ---- On 17 July 2025, students from Aleppo University organized a protest at Aleppo - University of Aleppo in Aleppo city to condemn the crimes committed by the militias of Hikmat al-Hijri against Bedouin tribes in As-Sweida. ---- On 17 July 2025, student rioters attacked Druze students at the University of Aleppo in Aleppo - University of Aleppo neighborhood in Aleppo city amid rising tensions and following recent attacks on Bedouin tribes in As Sweida. Later, the president of the university addressed the students, calling for an end to the violence and urging them to calm the situation.</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2024-01-27 ---- 2024-09-11 ---- 2024-10-10 ---- 2025-05-24</t>
+          <t>2024-03-10 ---- 2024-03-20 ---- 2024-04-27 ---- 2024-09-07 ---- 2024-10-23 ---- 2024-10-29 ---- 2024-11-09 ---- 2024-11-28 ---- 2024-11-29 ---- 2024-11-29 ---- 2024-12-01 ---- 2024-12-02 ---- 2025-01-05 ---- 2025-02-25 ---- 2025-03-26 ---- 2025-04-08 ---- 2025-04-28 ---- 2025-05-18 ---- 2025-06-01 ---- 2025-07-06 ---- 2025-07-17 ---- 2025-07-17</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Afrin</t>
+          <t>Jebel Saman</t>
         </is>
       </c>
       <c r="AQ3" t="n">
@@ -974,101 +908,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SY0204</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2024-06-13</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>June 2024: Three young girls including a sixteen-year-old girl, were detained for conscription by PKK's YDG-H (Al Shabiba Al Thawria) members, while going to an educational course.</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>NSA</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Kurdistan Workers' Party</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Firearms</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
+          <t>SY0202</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>NoInformation</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
@@ -1076,10 +944,10 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1089,47 +957,47 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Protests ---- Protests ---- Violence against civilians ---- Violence against civilians ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Violence against civilians ---- Protests</t>
+          <t>Violence against civilians ---- Explosions/Remote violence ---- Protests</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Peaceful protest ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Attack ---- Peaceful protest</t>
+          <t>Abduction/forced disappearance ---- Shelling/artillery/missile attack ---- Peaceful protest</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Protesters (Syria) ---- Protesters (Syria) ---- PKK: Kurdistan Workers Party ---- PKK: Kurdistan Workers Party ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria)</t>
+          <t>National Police Forces ---- YPG: Peoples Protection Units ---- Protesters (Syria)</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Students (Syria) ---- Students (Syria) ---- YDG-H: Patriotic Revolutionary Youth Movement ---- YDG-H: Patriotic Revolutionary Youth Movement ---- Students (Syria) ---- Students (Syria) ---- Students (Syria) ---- Students (Syria) ---- Students (Syria) ---- Students (Syria) ---- Teachers (Syria) ---- Teachers (Syria)</t>
+          <t>Students (Syria)</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+          <t>Civilians (Syria) ---- Civilians (Syria)</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Students (Syria); Women (Syria) ---- Refugees/IDPs (Syria); Students (Syria); Women (Syria)</t>
+          <t>Teachers (Syria)</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>On 28 April 2024, students staged a protest at the campus of the Free University of Aleppo in the city of Azaz in the countryside of Aleppo, demanding the construction of a university hospital to train students. ---- On 13 May 2024, students of the Free University of Aleppo staged a protest in the city of Azaz, denouncing the Israeli assault on Gaza strip and in support of Palestinians. ---- On 13 June 2024, PKK's YDG-H (Al Shabiba Al Thawria) members detained three young girls including a sixteen-year-old girl while she was going to an educational course in Ahras town in Aleppo countryside for conscription. ---- On 16 June 2024, PKK-affiliated Patriotic Revolutionary Youth Movement kidnapped a young displaced female student from Barkhadan Camp in the countryside of Aleppo for conscription. ---- On 1 July 2024, students staged a protest inside Shaam university in the city of Azaz in the countryside of Aleppo against the opening of a new crossing between JWS-controlled areas and Syrian regime-controlled areas in Abu Zandin. ---- On 8 September 2024, students staged a protest at Free Aleppo University campus in the city of Azaz in the countryside of Aleppo against the education policies of the Syrian Interim Government. ---- On 13 October 2024, students staged a protest at the Free Aleppo University campus in the city of Azaz in the countryside of Aleppo, opposing the decision to cancel the teaching of two departments at the university. ---- On 7 April 2025, university students staged a protest at the Free University of Aleppo campus in Azaz city in the countryside of Aleppo, against the Israeli attacks on the Gaza Strip and in support of the Palestinian people. ---- On 28 April 2025, students staged a protest at the Free University of Aleppo campus in the city of Azaz in the countryside of Aleppo, demanding a reduction in university fees. ---- On 28 April 2025, students staged a protest at the Free University of Aleppo campus in the town of Mare' in the countryside of Aleppo, demanding a reduction in university fees. ---- On 9 July 2025, teachers of men and women staged a protest in front of the education directorate building in Azaz town in Aleppo countryside, demanding the improvement of the professional and living conditions of teaching staff, and the permanent appointment of workers in the education sector without additional conditions. ---- On 30 July 2025, six unknown gunmen pretending to be police forces surrounded a school manager's house in Kafin town in Aleppo countryside, and tried to break into it, and opened fire at the house's door while closed, killing an elderly woman, and injuring three children one of whom is seven-year-old. 1 fatality. ---- On 8 August 2025, teachers staged a protest in Al Hurriyah square in Aghtrin town in Aleppo countryside, demanding to be included in the staff of the Ministry of Education in the Syrian government and that their living conditions be improved.</t>
+          <t>On 26 March 2024, national police forces detained the principal of the Baraem Al Iman Institute and his son in the town of Al Bab in the countryside of Aleppo, for unknown reasons. ---- On 24 November 2024, YPG artillery and rocket shelling targeted a residential building near a school in Al Bab city in the countryside of Aleppo, killing two civilians, wounding 12 others and causing material damage. 2 fatalities. ---- On 12 May 2025, students staged a protest in the city of Al Bab in the countryside of Aleppo, rejecting the Ministry of Education's decision to limit exam centers to the city of Aleppo. They stated that the decision would increase students' expenses related to travel and accommodation.</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2024-04-28 ---- 2024-05-13 ---- 2024-06-13 ---- 2024-06-16 ---- 2024-07-01 ---- 2024-09-08 ---- 2024-10-13 ---- 2025-04-07 ---- 2025-04-28 ---- 2025-04-28 ---- 2025-07-09 ---- 2025-07-30 ---- 2025-08-08</t>
+          <t>2024-03-26 ---- 2024-11-24 ---- 2025-05-12</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Azaz</t>
+          <t>Al Bab</t>
         </is>
       </c>
       <c r="AQ4" t="n">
@@ -1139,11 +1007,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SY0205</t>
+          <t>SY0203</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1158,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1170,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1191,44 +1059,48 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2025-01-31 ---- 2025-01-29 ---- 2025-01-18</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>January 2025: An education facility was hit by Turkish airstrikes. ---- January 2025: A car bomb detonated in front of a health facility and education facility, killing one person and injuring seven others. ---- January 2025: An education facility was almost completely destroyed by Turkish Air Forces during a wider bomb attack over two villages.</t>
+          <t>October 2024: An educator was arrested at their home by the Syrian National Army (SNA) on accusations that they were working with the SDF.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Building  ---- Private Travel ---- Education Building </t>
+          <t>Home</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Foreign Forces - Military ---- No Information ---- Foreign Forces - Military</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Armed Forces of Turkey ---- No Information ---- Armed Forces of Turkey</t>
+          <t>Syrian National Army (SNA)</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aerial Bomb: Plane ---- VBIED ---- Aerial Bomb: Plane</t>
+          <t>No Information on the Weapon Used</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>NoInformation</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
@@ -1237,10 +1109,10 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1250,43 +1122,47 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Protests ---- Violence against civilians ---- Riots ---- Explosions/Remote violence ---- Violence against civilians ---- Violence against civilians ---- Protests ---- Protests ---- Protests</t>
+          <t>Violence against civilians ---- Protests ---- Violence against civilians ---- Protests</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Protest with intervention ---- Abduction/forced disappearance ---- Violent demonstration ---- Remote explosive/landmine/IED ---- Attack ---- Attack ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest</t>
+          <t>Abduction/forced disappearance ---- Peaceful protest ---- Abduction/forced disappearance ---- Peaceful protest</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Protesters (Syria) ---- QSD: Syrian Democratic Forces ---- Rioters (Syria) ---- QSD: Syrian Democratic Forces ---- Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria)</t>
+          <t>National Police Forces ---- Protesters (Syria) ---- National Police Forces ---- Protesters (Syria)</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Teachers (Syria) ---- Teachers (Syria) ---- Teachers (Syria)</t>
+          <t>Students (Syria) ---- Students (Syria)</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>QSD: Syrian Democratic Forces ---- Civilians (Syria) ---- Asayish (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr"/>
+          <t>Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Teachers (Syria) ---- Teachers (Syria)</t>
+        </is>
+      </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>On 12 October 2024, residents held a protest in Menbij city in Aleppo's countryside condemning the DFNS' imposition of an educational curricula amidst calls for a strike to be held. QSD fighters attempted to prevent attendees from reaching Menbij city to participate by closing city squares and roads. Schools were also closed in the city for the second week in a row. ---- On 12 October 2024, QSD forces detained a 33-year-old man from his residence in the al-Sarb neighborhood in northern Menbij city (Aleppo). The arrest was due to his participation in anti-QSD protests criticizing the education curriculum imposed by the group. He was taken to an undisclosed location. ---- On 14 October 2024, dozens of locals staged a demonstration in the city of Menbij in the countryside of Aleppo against the new curriculum imposed by DFNS on schools. The demonstrators threw stones at Asayish patrols, who detained several participants before later releasing them. ---- On 23 January 2025, a booby-trapped vehicle planted by QSD detonated in front of a school in Menbij town in Aleppo's countryside, killing one man who is driver from Menbij, and injuring five others. 1 fatality. ---- Around 25 January 2025 (week of), the body of a young man was found with signs of a gunshot wound in a school's courtyard in Menbij city in rural southern Aleppo, killed by unidentified gunmen for unknown reasons. The victim is from Hiymar Jis village. 1 fatality. ---- On 27 March 2025, unknown gunmen shot and killed a young man who was riding a motorcycle with a friend near Al 'abbas school in the outskirts of Menbij city in Aleppo's countryside. The victim is from Menbij city. 1 fatality. ---- On 19 June 2025, teachers staged a protest in front of the educational community building in Menbij town in Aleppo countryside, demanding to improve their working conditions, and the payment of their salaries which are six months late. ---- On 28 June 2025, teachers staged a protest in the city of Menbij in the countryside of Aleppo, denouncing the lack of permanent employment and the delay in disbursing their salaries. ---- On 6 July 2025, teachers staged a protest in the city of Menbij in the countryside of Aleppo, opposing the Minister of Education and the policies he is implementing.</t>
+          <t>Around 27 January 2024 (week of), National Police Forces detained a forty-seven-year-old teacher who is from Turandah village in rural Aleppo for ransom after an IDP filed a complaint against the teacher over the sale of a newspaper business. The victims' whereabouts remain unknown. ---- On 11 September 2024, dozens of locals including students staged a protest in Afrin town in Aleppo countryside, and demanded a National Police Forces officer to be referred for investigation, after he stormed Omar Bin Al Khattab school in the town, arrested the school principal, and assaulted the teaching staff for not giving books to his son. ---- On 10 October 2024, National police forces detained a teacher in the village of Kafr Safra in the countryside of Jandairis (Afrin, Aleppo) on allegations of espionage for the QSD. ---- On 24 May 2025, students and their families staged a protest in the city of Afrin in the countryside of Aleppo for the second consecutive day, in rejection of the recent decision issued by the Ministry of Education to designate Aleppo as the sole center for conducting exams.</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2024-10-12 ---- 2024-10-12 ---- 2024-10-14 ---- 2025-01-23 ---- 2025-01-25 ---- 2025-03-27 ---- 2025-06-19 ---- 2025-06-28 ---- 2025-07-06</t>
+          <t>2024-01-27 ---- 2024-09-11 ---- 2024-10-10 ---- 2025-05-24</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Menbij</t>
+          <t>Afrin</t>
         </is>
       </c>
       <c r="AQ5" t="n">
@@ -1296,7 +1172,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SY0207</t>
+          <t>SY0204</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1318,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1339,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1352,17 +1228,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>April 2025: A former head of programme was shot and killed by a group of masked gunmen at a makeshift checkpoint.</t>
+          <t>June 2024: Three young girls including a sixteen-year-old girl, were detained for conscription by PKK's YDG-H (Al Shabiba Al Thawria) members, while going to an educational course.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t xml:space="preserve">Education Building </t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1372,7 +1248,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Unidentified Armed Actor</t>
+          <t>Kurdistan Workers' Party</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1386,7 +1262,11 @@
         </is>
       </c>
       <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>NoInformation</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1397,7 +1277,7 @@
         <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1407,39 +1287,47 @@
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Protests ---- Protests ---- Violence against civilians ---- Violence against civilians ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Violence against civilians ---- Protests</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Peaceful protest ---- Peaceful protest ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Attack ---- Peaceful protest</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>Unidentified Armed Group (Syria)</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr"/>
+          <t>Protesters (Syria) ---- Protesters (Syria) ---- PKK: Kurdistan Workers Party ---- PKK: Kurdistan Workers Party ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria)</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Students (Syria) ---- Students (Syria) ---- YDG-H: Patriotic Revolutionary Youth Movement ---- YDG-H: Patriotic Revolutionary Youth Movement ---- Students (Syria) ---- Students (Syria) ---- Students (Syria) ---- Students (Syria) ---- Students (Syria) ---- Students (Syria) ---- Teachers (Syria) ---- Teachers (Syria)</t>
+        </is>
+      </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Civilians (Syria)</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr"/>
+          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Students (Syria); Women (Syria) ---- Refugees/IDPs (Syria); Students (Syria); Women (Syria)</t>
+        </is>
+      </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>On 9 April 2025, unknown masked gunmen stopped a former religious school director at a temporary checkpoint on Al Waha road on the outskirts of As-Safira town in eastern Aleppo countryside, and shot and killed him. The victim was known for his loyalty to the former regime and alleged ties to its security services. 1 fatality.</t>
+          <t>On 28 April 2024, students staged a protest at the campus of the Free University of Aleppo in the city of Azaz in the countryside of Aleppo, demanding the construction of a university hospital to train students. ---- On 13 May 2024, students of the Free University of Aleppo staged a protest in the city of Azaz, denouncing the Israeli assault on Gaza strip and in support of Palestinians. ---- On 13 June 2024, PKK's YDG-H (Al Shabiba Al Thawria) members detained three young girls including a sixteen-year-old girl while she was going to an educational course in Ahras town in Aleppo countryside for conscription. ---- On 16 June 2024, PKK-affiliated Patriotic Revolutionary Youth Movement kidnapped a young displaced female student from Barkhadan Camp in the countryside of Aleppo for conscription. ---- On 1 July 2024, students staged a protest inside Shaam university in the city of Azaz in the countryside of Aleppo against the opening of a new crossing between JWS-controlled areas and Syrian regime-controlled areas in Abu Zandin. ---- On 8 September 2024, students staged a protest at Free Aleppo University campus in the city of Azaz in the countryside of Aleppo against the education policies of the Syrian Interim Government. ---- On 13 October 2024, students staged a protest at the Free Aleppo University campus in the city of Azaz in the countryside of Aleppo, opposing the decision to cancel the teaching of two departments at the university. ---- On 7 April 2025, university students staged a protest at the Free University of Aleppo campus in Azaz city in the countryside of Aleppo, against the Israeli attacks on the Gaza Strip and in support of the Palestinian people. ---- On 28 April 2025, students staged a protest at the Free University of Aleppo campus in the city of Azaz in the countryside of Aleppo, demanding a reduction in university fees. ---- On 28 April 2025, students staged a protest at the Free University of Aleppo campus in the town of Mare' in the countryside of Aleppo, demanding a reduction in university fees. ---- On 9 July 2025, teachers of men and women staged a protest in front of the education directorate building in Azaz town in Aleppo countryside, demanding the improvement of the professional and living conditions of teaching staff, and the permanent appointment of workers in the education sector without additional conditions. ---- On 30 July 2025, six unknown gunmen pretending to be police forces surrounded a school manager's house in Kafin town in Aleppo countryside, and tried to break into it, and opened fire at the house's door while closed, killing an elderly woman, and injuring three children one of whom is seven-year-old. 1 fatality. ---- On 8 August 2025, teachers staged a protest in Al Hurriyah square in Aghtrin town in Aleppo countryside, demanding to be included in the staff of the Ministry of Education in the Syrian government and that their living conditions be improved.</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2024-04-28 ---- 2024-05-13 ---- 2024-06-13 ---- 2024-06-16 ---- 2024-07-01 ---- 2024-09-08 ---- 2024-10-13 ---- 2025-04-07 ---- 2025-04-28 ---- 2025-04-28 ---- 2025-07-09 ---- 2025-07-30 ---- 2025-08-08</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>As Safira</t>
+          <t>Azaz</t>
         </is>
       </c>
       <c r="AQ6" t="n">
@@ -1449,11 +1337,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SY0307</t>
+          <t>SY0205</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -1465,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1495,112 +1383,108 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2025-01-31 ---- 2025-01-29 ---- 2025-01-18</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>January 2024: Syrian regime forces arrested two college students after storming their dormitory.</t>
+          <t>January 2025: An education facility was hit by Turkish airstrikes. ---- January 2025: A car bomb detonated in front of a health facility and education facility, killing one person and injuring seven others. ---- January 2025: An education facility was almost completely destroyed by Turkish Air Forces during a wider bomb attack over two villages.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t xml:space="preserve">Education Building  ---- Private Travel ---- Education Building </t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Foreign Forces - Military ---- No Information ---- Foreign Forces - Military</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Syrian Public Security Police</t>
+          <t>Armed Forces of Turkey ---- No Information ---- Armed Forces of Turkey</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Firearms</t>
+          <t>Aerial Bomb: Plane ---- VBIED ---- Aerial Bomb: Plane</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Secondary School</t>
+          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>NoInformation</t>
-        </is>
-      </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rural Damascus</t>
+          <t>Aleppo</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>SY03</t>
+          <t>SY02</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Strategic developments</t>
+          <t>Protests ---- Violence against civilians ---- Riots ---- Explosions/Remote violence ---- Violence against civilians ---- Violence against civilians ---- Protests ---- Protests ---- Protests</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Arrests</t>
+          <t>Protest with intervention ---- Abduction/forced disappearance ---- Violent demonstration ---- Remote explosive/landmine/IED ---- Attack ---- Attack ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Police Forces of Syria (2000-2024) General Intelligence Directorate</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr"/>
+          <t>Protesters (Syria) ---- QSD: Syrian Democratic Forces ---- Rioters (Syria) ---- QSD: Syrian Democratic Forces ---- Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria)</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Teachers (Syria) ---- Teachers (Syria) ---- Teachers (Syria)</t>
+        </is>
+      </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Civilians (Syria)</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Students (Syria)</t>
-        </is>
-      </c>
+          <t>QSD: Syrian Democratic Forces ---- Civilians (Syria) ---- Asayish (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>On 22 January 2024, unspecified Syrian intelligence branch arrested two university students in city of Az-Zabdani in Rural Damascus for unknown reasons.</t>
+          <t>On 12 October 2024, residents held a protest in Menbij city in Aleppo's countryside condemning the DFNS' imposition of an educational curricula amidst calls for a strike to be held. QSD fighters attempted to prevent attendees from reaching Menbij city to participate by closing city squares and roads. Schools were also closed in the city for the second week in a row. ---- On 12 October 2024, QSD forces detained a 33-year-old man from his residence in the al-Sarb neighborhood in northern Menbij city (Aleppo). The arrest was due to his participation in anti-QSD protests criticizing the education curriculum imposed by the group. He was taken to an undisclosed location. ---- On 14 October 2024, dozens of locals staged a demonstration in the city of Menbij in the countryside of Aleppo against the new curriculum imposed by DFNS on schools. The demonstrators threw stones at Asayish patrols, who detained several participants before later releasing them. ---- On 23 January 2025, a booby-trapped vehicle planted by QSD detonated in front of a school in Menbij town in Aleppo's countryside, killing one man who is driver from Menbij, and injuring five others. 1 fatality. ---- Around 25 January 2025 (week of), the body of a young man was found with signs of a gunshot wound in a school's courtyard in Menbij city in rural southern Aleppo, killed by unidentified gunmen for unknown reasons. The victim is from Hiymar Jis village. 1 fatality. ---- On 27 March 2025, unknown gunmen shot and killed a young man who was riding a motorcycle with a friend near Al 'abbas school in the outskirts of Menbij city in Aleppo's countryside. The victim is from Menbij city. 1 fatality. ---- On 19 June 2025, teachers staged a protest in front of the educational community building in Menbij town in Aleppo countryside, demanding to improve their working conditions, and the payment of their salaries which are six months late. ---- On 28 June 2025, teachers staged a protest in the city of Menbij in the countryside of Aleppo, denouncing the lack of permanent employment and the delay in disbursing their salaries. ---- On 6 July 2025, teachers staged a protest in the city of Menbij in the countryside of Aleppo, opposing the Minister of Education and the policies he is implementing.</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-10-12 ---- 2024-10-12 ---- 2024-10-14 ---- 2025-01-23 ---- 2025-01-25 ---- 2025-03-27 ---- 2025-06-19 ---- 2025-06-28 ---- 2025-07-06</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Az Zabdani</t>
+          <t>Menbij</t>
         </is>
       </c>
       <c r="AQ7" t="n">
@@ -1610,166 +1494,84 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SY0401</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>4</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>2025-05-05 ---- 2025-04-27 ---- 2025-04-20 ---- 2025-03-04</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>May 2025: An educator was arrested from his house by members of the general security forces. ---- April 2025: A student was kidnapped from an education facility by and unidentified armed group after being lured there by a staffer. Her father was arrested 10 days later, on the 11th day she was released. Thought to be marriage related incident. ---- April 2025: A head of programme was shot and killed by unidentified gunmen in his home. ---- March 2025: An educator was kidnapped by gunmen who claimed to belong to the Internal Security. His body was found the following day with gunshot wounds to the head.</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Home ---- Education Building  ---- Home ---- Unspecified Location</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Police ---- NSA ---- NSA ---- Police</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Syrian Public Security Police ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Syrian Public Security Police</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Firearms ---- Firearms ---- Firearms ---- Firearms</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Not Applicable ---- School: No Further Details ---- Not Applicable ---- Not Applicable</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>NoInformation ---- Killed</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Freed</t>
-        </is>
-      </c>
+          <t>SY0206</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Homs</t>
+          <t>Aleppo</t>
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SY02</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Strategic developments ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Explosions/Remote violence ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Riots ---- Violence against civilians ---- Strategic developments ---- Violence against civilians</t>
+          <t>Explosions/Remote violence ---- Explosions/Remote violence</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Attack ---- Arrests ---- Abduction/forced disappearance ---- Attack ---- Attack ---- Grenade ---- Attack ---- Attack ---- Attack ---- Attack ---- Mob violence ---- Attack ---- Arrests ---- Attack</t>
+          <t>Air/drone strike ---- Air/drone strike</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>Military Forces of Syria (2000-2024) Prison Guards ---- Police Forces of Syria (2000-2024) ---- Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Police Forces of Syria (2024-) ---- Police Forces of Syria (2024-) ---- Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Rioters (Syria) ---- Unidentified Armed Group (Syria) ---- Police Forces of Syria (2024-) ---- Unidentified Armed Group (Syria)</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Students (Syria)</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Prisoners (Syria); Students (Syria) ---- Students (Syria) ---- Teachers (Syria); Women (Syria) ---- Teachers (Syria) ---- Alawite Muslim Group (Syria); Former QDW: National Defence Forces; Students (Syria) ---- Alawite Muslim Group (Syria) ---- Students (Syria) ---- Students (Syria) ---- Alawite Muslim Group (Syria) ---- Teachers (Syria) ---- Druze Group (Syria); Students (Syria) ---- Alawite Muslim Group (Syria); Teachers (Syria) ---- Teachers (Syria) ---- Alawite Muslim Group (Syria); Students (Syria)</t>
-        </is>
-      </c>
+          <t>Military Forces of Turkey (2016-) ---- Military Forces of Turkey (2016-)</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Around 5 February 2024 (month of), a student died under torture after being in detention since 2014 in one of the regime prisons in Homs, coded to Homs - Central Prison. The student hailed from Madiq Castle. 1 fatality. ---- On 9 March 2024, Syrian regime police detained a 9-year-old child from his school in the village of Marj al Qata in the countryside of Homs for distorting the picture of Bashar Al Assad by drawing on it in his textbook. Additionally, the school principal physically assaulted the child for doing so. ---- On 20 January 2025, an unidentified armed group kidnapped a woman in the city of Homs for unknown reasons. The abductee is an Assistant Professor at the University of Homs. ---- On 5 March 2025, a man's body with gunshot marks was found in Al-Waer neighborhood in Homs - Al-Waer city, killed by unknown gunmen pretending to be police forces after they kidnapped him the previous day. The man was a PE teacher. 1 fatality. ---- On 20 March 2025, unknown gunmen raided a house in Al Iddikhar neighborhood in Homs city, killing a 50-year-old man and his three sons, all members of the Alawite sect. The father had previously worked in construction in Algeria before returning to Syria. His sons included a 22-year-old former QDW member and two 19-year-old high school students. 4 fatalities. ---- On 2 April 2025, an unknown gunman on a motorbike threw a hand grenade at an Alawite family near a school in Homs - Karm al-Louz neighborhood in Homs city, killing a child, and injuring four people; a man, his wife, and their two children. 1 fatality. ---- On 25 April 2025, police forces raided a university student's house in Homs - Karm al-Louz neighborhood in Homs city, and arrested him for unknown reasons. On the same day, they raided a driver's house in the same neighborhood and arrested him for unknown reasons. The student's body was found later in Al Nahda hospital killed by presumably police forces, and the driver's body was also found in Al Waleed hospital killed by presumably police forces as well. 2 fatalities. ---- On 25 April 2025, three masked police members raided a university student's house in Homs - Nuzha neighborhood in Homs city, and arrested him for unknown reasons. They also threatened to kill his sick mother if anyone tries to go out to the balcony. The student's body was found later in a hospital killed by presumably police forces. In another incident police forces detained another man from his house in the same neighborhood, and his body was also found later near his house. 2 fatalities. ---- On 25 April 2025, residents found the body of a 58-year-old man from the Alawite sect near a School in Homs - Karm al-Zeitoun neighborhood of Homs city. The victim, who owned a grocery store in the same neighborhood, had been abducted earlier that day by unidentified gunmen from in front of his home. 1 fatality. ---- Around 26 April 2025 (as reported), the body of a teacher was found at Al-Basel Hospital in Homs city, killed by an unidentified armed group for unknown reasons. He had been reported missing two days earlier while on his way home in Wadi al-Thahab neighbourhood. 1 fatality. ---- On 28 April 2025, students at the dormitory of Homs University in Homs city stormed several rooms belonging to students from As-Sweida province, wounding one student with a gunshot amid sectarian chants. The incident occurred after a voice recording circulated among locals, allegedly featuring a Druze military commander from As-Sweida cursing the Prophet, which sparked widespread outrage. Police forces intervened to disperse the students and restore order. ---- On 3 May 2025, an unidentified armed group shot and killed a woman and wounded her husband and two children in Homs - Wadi al-Thahab neighborhood in Homs city for unknown reasons. Both victims were Alawite and the woman was a teacher. 1 fatality. ---- On 5 May 2025, Syrian police members arrested an Al Baath University professor at his home in Homs - Karm al-Zeitoun neighborhood in the city of Homs for unknown reasons. ---- Around 12 July 2025 (week of), an unidentified armed group shot and wounded a university student from Alawite community in Homs - Karm al-Louz neighborhood of Homs city. He succumbed to his injuries on 26 July. 1 fatality.</t>
+          <t>On 18 January 2025, Turkish warplanes conducted airstrikes targeting a school in the village of Jaadet Elsamawat in the countryside of Aleppo. Casualties unknown. ---- On 31 January 2025, Turkish warplanes conducted airstrikes targeting a school in Khrus town in Aleppo countryside. Casualties unknown.</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>2024-02-05 ---- 2024-03-09 ---- 2025-01-20 ---- 2025-03-05 ---- 2025-03-20 ---- 2025-04-02 ---- 2025-04-25 ---- 2025-04-25 ---- 2025-04-25 ---- 2025-04-26 ---- 2025-04-28 ---- 2025-05-03 ---- 2025-05-05 ---- 2025-07-12</t>
+          <t>2025-01-18 ---- 2025-01-31</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Homs</t>
+          <t>Ain Al Arab</t>
         </is>
       </c>
       <c r="AQ8" t="n">
@@ -1779,11 +1581,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SY0600</t>
+          <t>SY0207</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1798,10 +1600,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1835,37 +1637,37 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">August 2024: A school was hit and damaged by shelling by Syria regime forces. The school was out of service due to the displacement of the village's residents. </t>
+          <t>April 2025: A former head of programme was shot and killed by a group of masked gunmen at a makeshift checkpoint.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Building </t>
+          <t>Other</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Syrian Armed Forces</t>
+          <t>Unidentified Armed Actor</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Shelling</t>
+          <t>Firearms</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>School: No Further Details</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr"/>
@@ -1873,64 +1675,56 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lattakia</t>
+          <t>Aleppo</t>
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>SY06</t>
+          <t>SY02</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Strategic developments ---- Violence against civilians ---- Protests ---- Violence against civilians ---- Battles</t>
+          <t>Violence against civilians</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Air/drone strike ---- Shelling/artillery/missile attack ---- Other ---- Attack ---- Peaceful protest ---- Attack ---- Armed clash</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Civilians (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Police Forces of Syria (2024-) ---- Anti-Military Operations Command Militia (Syria)</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Turkmen Communal Group (Syria) ---- Teachers (Syria) ---- Ministry of Defense of the Syrian Interim Government</t>
-        </is>
-      </c>
+          <t>Unidentified Armed Group (Syria)</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Police Forces of Syria (2024-)</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Teachers (Syria) ---- Students (Syria) ---- Labor Group (Syria)</t>
-        </is>
-      </c>
+          <t>Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>On 17 March 2024, Syrian regime forces conducted a suicide drone attack near a school in the village of Yamdiyeh in the countryside of Lattakia. There were no casualties. ---- On 3 August 2024, regime fighters shelled a school in Nawwara-Klz (Klz) village in rural Lattakia, causing material damage without causing any casualties. The school was out of service due to the displacement of the village's residents. ---- Other: On 21 December 2024, local residents who are majority Turkmen group members expelled non-Turkmen teachers and the school's principal from a school in Al Issawiyya in rural Lattakia over sectarian affiliations. Teachers accused unspecified groups who are loyal to Turkey of pressuring residents to expel non-Turkmen teachers. The new regime has not taken any action in response. ---- On 26 December 2024, unknown gunmen shot and killed a student in the faculty of medicine in Lattakia city. 1 fatality. ---- On 23 January 2025, tens of teachers staged a protest in front of the education directorate building in Lattakia city, against the decision of ending the duty location and returning them to their areas of origin. ---- On 4 March 2025, Syrian police members conducted a security operation in Lattakia - Da'tor neighborhood and several other neighborhoods in Lattakia city targeting former regime remnants, during which they shot several civilians, killing four of them including two school guards and arresting several wanted individuals. On the same day, the Ministry of Defense of the Syrian Interim Government deployed vehicles equipped with machine guns to the vicinity of the neighborhood in search of drug dealers, former regime remnants and individuals who escaped from prisons. 4 fatalities. ---- On 6 March 2025, an Anti-Military Operations Command militia attacked the headquarters of the General Security Forces (police forces) in Lattakia - Teshreen Suburb neighborhood in Lattakia city. One of the attackers was killed, and three others were arrested. During the clashes, one university student was killed. 2 fatalities.</t>
+          <t>On 9 April 2025, unknown masked gunmen stopped a former religious school director at a temporary checkpoint on Al Waha road on the outskirts of As-Safira town in eastern Aleppo countryside, and shot and killed him. The victim was known for his loyalty to the former regime and alleged ties to its security services. 1 fatality.</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>2024-03-17 ---- 2024-08-03 ---- 2024-12-21 ---- 2024-12-26 ---- 2025-01-23 ---- 2025-03-04 ---- 2025-03-06</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Lattakia</t>
+          <t>As Safira</t>
         </is>
       </c>
       <c r="AQ9" t="n">
@@ -1940,158 +1734,96 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SY0700</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2024-09-15 ---- 2024-08-21 ---- 2024-03-19 ---- 2024-03-19 ---- 2024-01-07 ---- 2024-01-05</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>September 2024: A school was damaged by Syrian forces shelling on the area. A child and a young man were injured. ---- August 2024: A school was hit when Syrian regime forces shelled the area.  ---- March 2024: An elementary school was hit by Syrian regime forces rockets, partially destroying it. ---- March 2024: An elementary school and homes were hit by Syrian regime forces rockets. ---- January 2024: Syrian forces targeted a school-turned-shelter with incendiary weapons. One civilian sustained burns, whilst three others got wounded by missile shrapnel. ---- January 2024: Government forces attacked a school, injuring a child, who later died of their injuries.</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Other ---- Other ---- Other ---- Other ---- Other ---- Other</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Shelling ---- Shelling ---- Rocket ---- Rocket ---- Missile ---- Artillery</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>School: No Further Details ---- School: No Further Details ---- Primary School ---- Primary School ---- School: No Further Details ---- School: No Further Details</t>
-        </is>
-      </c>
+          <t>SY0208</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Idleb</t>
+          <t>Aleppo</t>
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>SY07</t>
+          <t>SY02</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Explosions/Remote violence ---- Protests ---- Protests ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Protests ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Protests ---- Protests</t>
+          <t>Protests ---- Violence against civilians ---- Protests ---- Explosions/Remote violence ---- Protests ---- Protests ---- Protests ---- Protests</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Shelling/artillery/missile attack ---- Peaceful protest ---- Peaceful protest ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Peaceful protest ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Peaceful protest ---- Peaceful protest</t>
+          <t>Peaceful protest ---- Attack ---- Peaceful protest ---- Shelling/artillery/missile attack ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Military Forces of Syria (2000-2024) ---- Protesters (Syria) ---- Protesters (Syria) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Protesters (Syria) ---- Military Forces of Russia (2000-) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Russia (2000-) ---- Protesters (Syria) ---- Protesters (Syria)</t>
+          <t>Protesters (Syria) ---- AAS: Ahrar al Sham ---- Protesters (Syria) ---- QSD: Syrian Democratic Forces ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria)</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Teachers (Syria) ---- Students (Syria) ---- Students (Syria) ---- Teachers (Syria) ---- Students (Syria) ---- Teachers (Syria) ---- Teachers (Syria) ---- Students (Syria) ---- Students (Syria) ---- Teachers (Syria) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Teachers (Syria) ---- Teachers (Syria)</t>
+          <t>Students (Syria) ---- Labor Group (Syria); Students (Syria); Teachers (Syria) ---- Refugees/IDPs (Syria); Teachers (Syria) ---- Students (Syria) ---- Students (Syria) ---- Teachers (Syria)</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+          <t>Civilians (Syria) ---- Civilians (Syria)</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Refugees/IDPs (Syria); Teachers (Syria) ---- Students (Syria); Teachers (Syria) ---- Teachers (Syria); Students (Syria) ---- Students (Syria); Teachers (Syria) ---- Health Workers (Syria); Refugees/IDPs (Syria); Students (Syria); Teachers (Syria)</t>
+          <t>Students (Syria) ---- Students (Syria); Teachers (Syria); Health Workers (Syria)</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>On 3 January 2024, regime forces shelled a school in Afes town in Idleb countryside with artillery. A child died on 5th January from wounds sustained. 1 fatality. ---- On 19 March 2024, Syrian regime forces shelled a school in the village of Ketyan in the countryside of Idleb with rockets, causing only material damages. There were no casualties. ---- On 19 March 2024, Syrian regime forces shelled a school in the village of Toum in the countryside of Idleb with rockets, causing only material damages. There were no casualties. ---- On 1 April 2024, Syrian regime forces shelled a school in the town of Sarmin in the countryside of Idleb with rockets, killing a woman and a child, and wounding 9 civilians. 2 fatalities. ---- On 20 April 2024, tens of teachers organized a protest outside the directorate of education in the city of Idleb against their dismissals and calling for the decision to be overturned. ---- On 1 May 2024, students of the University of Idleb staged a protest in the city of Idleb, denouncing the Israeli assault on Gaza strip and in support of Palestinians. ---- On 4 May 2024, university students held a protest in front of the HTS-affiliated Syrian Salvation Government Prime Minister's office in Idleb city against the SSG's acceptance of graduates from regime-controlled areas into SSG institutions. ---- On 9 May 2024, teachers staged a protest in front of the Syrian Salvation Government building in the city of Idleb, demanding a rise in their salaries. ---- On 14 May 2024, twenty students who graduated from universities in Syrian regime-held areas staged a protest in front of the Syrian Salvation Government building in the city of Idleb, denouncing the decision to withdraw recognition of their diplomas. ---- On 16 May 2024, teachers organized a protest in front of Al Inkaz government building in Idleb city, demanding to improve living conditions, and to raise their salaries. ---- On 11 August 2024, teachers staged a protest in the city of Idleb against the decision to remove the French language from schools' curriculum. ---- On 21 August 2024, regime forces shelled Sarmin town including a school inside the town in Idleb countryside with heavy artillery. Casualties unknown. ---- On 31 August 2024, dozens of residents including students held a protest in front of Idleb University in Idleb city condemning the acceptance of students from regime-controlled areas in universities in northern Syria and their employment following their graduation. ---- On 4 September 2024, university students staged a protest in Idleb city, against appointing graduates of regime universities. ---- On 15 September 2024, Syrian regime forces shelled the town of Sarmin in the countryside of Idleb with artillery, wounding a child and a young man. Additionally, regime forces shelled a school in the town, causing material damage to the building. There were no fatalities. ---- On 16 November 2024, regime fighters shelled Teftnaz in rural Idleb with artillery, killing a displaced Quranic teacher from Saraqab and injuring three others. 1 fatality. ---- On 25 November 2024, teachers staged a protest against the Syrian Salvation Government in the city of Idleb, demanding a rise in their wages. ---- On 28 November 2024, Russian warplanes conducted airstrikes targeting the vicinity of Sarmin town in Idleb countryside in conjunction with regime fighters shelling a primary school in Sarmin city with rockets, injuring three civilians and causing material damage. There were no fatalities. ---- On 29 November 2024, Regime warplanes conducted airstrikes targeting two schools in Idleb city and its outskirts respectively and a nearby fuel station and water station in conjunction with regime fighters shelling the city with missiles, killing four civilians, wounding 19 others and causing material damage to the fuel station and a school. 4 fatalities. ---- On 1 December 2024, regime warplanes conducted several airstrikes throughout the day targeting several sites and facilities in Idleb city including three schools, a residential building in the outskirts of the city and near an ambulatory services center, killing fourteen civilians, including five children and a woman, wounding more than 59 others and causing material damage. 14 fatalities. ---- On 2 December 2024, Russian and regime warplanes carried out two airstrikes on a cluster of hospitals and health centers in the city of Idleb, and several airstrikes on a school, residential areas including Dawwar Shamma' and al Thawra neighborhoods as well as a refugee camp in Idleb city, killing twenty-one civilians including five women and eight children and wounding sixty-three other civilians including thirty children and twenty women. On 16 December, one individual died from injuries sustained. 22 fatalities. ---- On 25 February 2025, teachers held a protest in Idleb city calling to be reinstated to their teaching positions and payment of their suspended salaries after they were dismissed for participating in the Syrian revolution under the former regime. ---- On 5 July 2025, dozens of teachers staged a protest in the city of Idleb, denouncing a decision by the Minister of Education to reduce summer salaries from $150 to $90 per month.</t>
+          <t>On 26 April 2024, students staged a protest in the town of Jarablus in the countryside of Aleppo in solidarity with a female student who was killed in tribal armed clashes. ---- On 22 May 2024, Ahrar al Sham members pretending to be NPF detained a university student after raiding his house and beating him in Jarablus town in Aleppo countryside for unknown reasons. ---- On 29 May 2024, students and educational staff of Al Shari'a school staged a protest in Jarablus town in Aleppo countryside, against yesterday's attack by Northern Storm Brigade on the school. ---- On 16 October 2024, QSD fighters targeted a school and a health center in Muhsinli town in Aleppo countryside with rocket shelling, injuring six civilians including four students, a teacher, and a woman. There were no fatalities. ---- On 14 April 2025, internally displaced teachers staged a protest in Zoghra Camp in the countryside of Aleppo against the decision to suspend 60 teachers from their jobs. ---- On 23 May 2025, locals and students staged a protest in Jarablus town in Aleppo countryside, against the decision to make the centers for taking the intermediate and high school exams in the center of Aleppo city only, and that it will cost them a lot of transportation fees. ---- On 24 May 2025, dozens of students and their families staged a protest in the city of Jarablus in the countryside of Aleppo for the second consecutive day, in rejection of the recent decision issued by the Ministry of Education to designate Aleppo as the sole center for conducting exams. ---- On 3 July 2025, teachers staged a protest at Al Shuhada roundabout in Jarablus town in Aleppo countryside, to demand their appointment as official teachers and guarantee their job rights in accordance with the approved regulations and laws.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>2024-01-03 ---- 2024-03-19 ---- 2024-03-19 ---- 2024-04-01 ---- 2024-04-20 ---- 2024-05-01 ---- 2024-05-04 ---- 2024-05-09 ---- 2024-05-14 ---- 2024-05-16 ---- 2024-08-11 ---- 2024-08-21 ---- 2024-08-31 ---- 2024-09-04 ---- 2024-09-15 ---- 2024-11-16 ---- 2024-11-25 ---- 2024-11-28 ---- 2024-11-29 ---- 2024-12-01 ---- 2024-12-02 ---- 2025-02-25 ---- 2025-07-05</t>
+          <t>2024-04-26 ---- 2024-05-22 ---- 2024-05-29 ---- 2024-10-16 ---- 2025-04-14 ---- 2025-05-23 ---- 2025-05-24 ---- 2025-07-03</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Idleb</t>
+          <t>Jarablus</t>
         </is>
       </c>
       <c r="AQ10" t="n">
@@ -2101,112 +1833,98 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SY0702</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2024-02-21</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>February 2024: A school was damaged when Syrian regime forces shelled the area.</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Syrian Armed Forces</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Shelling</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>School: No Further Details</t>
-        </is>
-      </c>
+          <t>SY0301</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rural Damascus</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>SY03</t>
+        </is>
+      </c>
       <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Protests ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Attack ---- Peaceful protest ---- Other</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Druze Group (Syria); Refugees/IDPs (Syria); Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>On 30 January 2025, unidentified gunmen shot and killed a university student in Jdaydat al-Shaybani (Jdeidat al Wadi) in Rural Damascus for unknown reasons. On 1 February, locals discovered the victim's body in the Jdaydat al-Shaybani area. 1 fatality. ---- On 15 February 2025, locals staged a protest in the town of Jaramana in Rural Damascus, demanding the revelation of the whereabouts of a student who was kidnapped. ---- Other: On 29 April 2025, three buses carrying hundreds of students including Druze students from other Syrian provinces and several families from Jaramana in Rural Damascus departed the city following clashes which erupted over a circulated audio clip attributed to a Druze figure which is offensive to Muslims.</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>2025-01-30 ---- 2025-02-15 ---- 2025-04-29</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Rural Damascus</t>
+        </is>
+      </c>
       <c r="AQ11" t="n">
         <v>0</v>
       </c>
@@ -2214,158 +1932,88 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SY0703</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">June 2024: A educator was arrested by HTS personnel who raided his home over his participation in anti-HTS protests. He was taken to an undisclosed location. </t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>NSA</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Tahrir al-Sham</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Fist and Foot</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>NoInformation</t>
-        </is>
-      </c>
+          <t>SY0302</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Idleb</t>
+          <t>Rural Damascus</t>
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>SY07</t>
+          <t>SY03</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence</t>
+          <t>Battles</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Air/drone strike</t>
+          <t>Armed clash</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>Global Coalition Against Daesh</t>
+          <t>Unidentified Armed Group (Syria)</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Islamic State in Iraq and the Levant (ISIL)</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Civilians (Syria); Students (Syria)</t>
-        </is>
-      </c>
+          <t>Syrian Free Army</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>On 15 January 2025, Global Coalition targeted a motorbike with two suspected ISIL members on Al Qal'a camp road northwest of Sarmada town in Idleb countryside with a drone, killing them both, and injuring a student who was near the location. The student died from his wounds on 17th. 3 fatalities.</t>
+          <t>On 22 February 2024, unknown gunmen attacked a Syrian Free Army convoy and opened fire targeting one of its leaders in Rukban camp in rural Damascus during a ceremony honoring students. Casualties unknown.</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Harim</t>
+          <t>Duma</t>
         </is>
       </c>
       <c r="AQ12" t="n">
@@ -2375,154 +2023,88 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SY0705</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>7</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>2024-11-29 ---- 2024-11-26 ---- 2024-11-26 ---- 2024-01-22 ---- 2024-01-22 ---- 2024-01-18 ---- 2024-01-08</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>November 2024: A school was hit by Syrian and Russian airstrikes. ---- November 2024: An educational facility was damaged by Syrian regime forces shelling, killing and injuring an unspecified number of people including children.  ---- November 2024: A school was damaged by Syrian regime forces shelling, killing and injuring an unspecified number of people including children.  ---- January 2024: Rocket fired by Syrian regime forces struck and partially destroyed the perimeter fence of a school. ---- January 2024: Rocket fired by Syrian regime forces rocket struck and damaged the perimeter fence of a school, whilst students were taking exams. ---- January 2024: Two rockets fired by Syrian regime forces directly hit a school, partially destroying the building and damaging furniture. ---- January 2024: Shell fired by Syrian regime forces hit and partially destroyed the perimeter fence of an elementary school, a few hours after students had gone home.</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Other ---- Other ---- Other ---- Other ---- Other ---- Other ---- Other</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Syrian or Russian Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Aerial Bomb: Plane ---- Shelling ---- Shelling ---- Rocket ---- Rocket ---- Rocket ---- Shelling</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Secondary School ---- School: No Further Details ---- Primary School ---- Primary School</t>
-        </is>
-      </c>
+          <t>SY0306</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Idleb</t>
+          <t>Rural Damascus</t>
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>SY07</t>
+          <t>SY03</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence</t>
+          <t>Protests</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Air/drone strike</t>
+          <t>Peaceful protest</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024)</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Students (Syria); Teachers (Syria) ---- Students (Syria); Teachers (Syria)</t>
-        </is>
-      </c>
+          <t>Protesters (Syria)</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>On 8 January 2024, regime forces shelled the village of Eblin in the countryside of Idleb with artillery, and a shell fell on a school fence partially damaging it. Casualties unknown. ---- On 18 January 2024, regime forces shelled Mseibin town hitting a school with two rockets in Idleb countryside with artillery and rockets, partially damaging the school. Casualties unknown. ---- On 22 January 2024, Syrian regime forces shelled the town of Ariha partially damaging a school fence in the countryside of Idleb with rockets, wounding five civilians, including two children. There were no fatalities. ---- On 21 February 2024, regime forces shelled Bara town in Idleb countryside with artillery, a shell fell near a school causing only material damage. There were no casualties. ---- On 26 November 2024, Syrian regime forces shelled an educational center and a school in the town of Ariha in the countryside of Idleb with artillery, killing three civilians including two children, and wounding fourteen others. 2 fatalities. ---- On 29 November 2024, regime warplanes targeted a school and nearby house on the southeastern outskirts of Ferkia village in rural Idleb, injuring seven civilians including six children and causing material damage. There were no fatalities.</t>
+          <t>On 30 May 2025, students staged a protest in Qalamoun university in rural Damascus, against the visit of Dr. Salim Daboul, chairman of the board of directors of Al Nabras, which owns the private Qalamoun university. Protesters chanted slogans calling him 'shabiha' during his speech on freedom, and demanded that he and other figures of the former Asad regime be held accountable.</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>2024-01-08 ---- 2024-01-18 ---- 2024-01-22 ---- 2024-02-21 ---- 2024-11-26 ---- 2024-11-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Ariha</t>
+          <t>An Nabk</t>
         </is>
       </c>
       <c r="AQ13" t="n">
@@ -2532,7 +2114,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SY0800</t>
+          <t>SY0307</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2548,10 +2130,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2575,50 +2157,50 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2025-04-02 ---- 2024-12-12</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>April 2025: A student was abducted by PKK's YDG-H (Al Shabiba Al Thawria) members inside an educational facility. ---- December 2024: An education facility was destroyed by artillery fired by Turkish forces and Turkish-backed factions (JWS), operating under special operation forces.</t>
+          <t>January 2024: Syrian regime forces arrested two college students after storming their dormitory.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Building  ---- Education Building </t>
+          <t>Home</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>NSA ---- Multiple</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Kurdistan Workers' Party ---- Unidentified Armed Actor</t>
+          <t>Syrian Public Security Police</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Firearms ---- Artillery</t>
+          <t>Firearms</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Not Applicable ---- School: No Further Details</t>
+          <t>Secondary School</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr"/>
@@ -2630,64 +2212,60 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Al Hasakeh</t>
+          <t>Rural Damascus</t>
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>SY08</t>
+          <t>SY03</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Violence against civilians ---- Violence against civilians</t>
+          <t>Strategic developments</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance ---- Attack ---- Abduction/forced disappearance</t>
+          <t>Arrests</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>PKK: Kurdistan Workers Party ---- Unidentified Armed Group (Syria) ---- PKK: Kurdistan Workers Party</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>YDG-H: Patriotic Revolutionary Youth Movement ---- YDG-H: Patriotic Revolutionary Youth Movement</t>
-        </is>
-      </c>
+          <t>Police Forces of Syria (2000-2024) General Intelligence Directorate</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+          <t>Civilians (Syria)</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Women (Syria) ---- Teachers (Syria) ---- Students (Syria); Women (Syria)</t>
+          <t>Students (Syria)</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>On 6 March 2024, PKK's YDG-H (Al Shabiba Al Thawria) members detained a sixteen year old girl in front of Adnan Al Maliki school in Tal Tamer town in Al Hasakeh countryside presumably for conscription. ---- On 26 January 2025, an unidentified armed group shot and killed teacher at Al-Hubat crossing south of Al-Hasakeh city, for unknown reasons. 1 fatality. ---- On 2 April 2025, PKK's YDG-H (Al Shabiba Al Thawria) members abducted a sixteen-year-old girl in That Al Nitaqen school in Al Nasirah neighborhood in Al-Hasakeh city for conscription.</t>
+          <t>On 22 January 2024, unspecified Syrian intelligence branch arrested two university students in city of Az-Zabdani in Rural Damascus for unknown reasons.</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>2024-03-06 ---- 2025-01-26 ---- 2025-04-02</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>Al Hasakeh</t>
+          <t>Az Zabdani</t>
         </is>
       </c>
       <c r="AQ14" t="n">
@@ -2697,41 +2275,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SY0901</t>
+          <t>SY0401</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2740,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -2749,107 +2327,114 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2024-10-29 ---- 2024-10-22 ---- 2024-10-22 ---- 2024-02-14 ---- 2024-02-06 ---- 2024-01-26</t>
+          <t>2025-05-05 ---- 2025-04-27 ---- 2025-04-20 ---- 2025-03-04</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">October 2024: A school held by pro-Iran militia was hit by US airstrikes as part of the Global Coalition._x000D_
- ---- As reported in October 2024: An educational facility was occupied by the SDF military. ---- October 2024: An educational facility occupied by the SDF military was attacked by opposition forces. ---- February 2024: The SDF were stationed at a school. ---- February 2024: A college building which serves as a base for the Fatimyoun militia, was targeted by US strikes. ---- January 2024: educator executed by a firing squad belonging to an Islamic State cell. </t>
+          <t>May 2025: An educator was arrested from his house by members of the general security forces. ---- April 2025: A student was kidnapped from an education facility by and unidentified armed group after being lured there by a staffer. Her father was arrested 10 days later, on the 11th day she was released. Thought to be marriage related incident. ---- April 2025: A head of programme was shot and killed by unidentified gunmen in his home. ---- March 2025: An educator was kidnapped by gunmen who claimed to belong to the Internal Security. His body was found the following day with gunshot wounds to the head.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Unspecified Location</t>
+          <t>Home ---- Education Building  ---- Home ---- Unspecified Location</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Other ---- NSA ---- NSA ---- Host Government: Military ---- Other ---- NSA</t>
+          <t>Police ---- NSA ---- NSA ---- Police</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>International Coalition Forces in Syria ---- Syrian Democratic Forces ---- Unidentified Armed Actor ---- Syrian Democratic Forces ---- International Coalition Forces in Syria ---- Islamic State</t>
+          <t>Syrian Public Security Police ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Syrian Public Security Police</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aerial Bomb: Plane ---- No Information on the Weapon Used ---- Shelling ---- Firearms ---- Aerial Bomb: Plane ---- Firearms</t>
+          <t>Firearms ---- Firearms ---- Firearms ---- Firearms</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Not Applicable</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+          <t>Not Applicable ---- School: No Further Details ---- Not Applicable ---- Not Applicable</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>NoInformation ---- Killed</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Freed</t>
+        </is>
+      </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Deir ez Zor</t>
+          <t>Homs</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>SY09</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Strategic developments ---- Strategic developments ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Violence against civilians ---- Violence against civilians</t>
+          <t>Violence against civilians ---- Strategic developments ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Explosions/Remote violence ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Riots ---- Violence against civilians ---- Strategic developments ---- Violence against civilians</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance ---- Arrests ---- Change to group/activity ---- Grenade ---- Shelling/artillery/missile attack ---- Air/drone strike ---- Abduction/forced disappearance ---- Abduction/forced disappearance</t>
+          <t>Attack ---- Arrests ---- Abduction/forced disappearance ---- Attack ---- Attack ---- Grenade ---- Attack ---- Attack ---- Attack ---- Attack ---- Mob violence ---- Attack ---- Arrests ---- Attack</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Military Forces of Iran (1989-) Islamic Revolutionary Guard Corps ---- Police Forces of Syria (2000-2024) ---- QSD: Syrian Democratic Forces ---- Unidentified Armed Group (Syria) ---- Tribal and Clan Forces ---- Global Coalition Against Daesh ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces</t>
+          <t>Military Forces of Syria (2000-2024) Prison Guards ---- Police Forces of Syria (2000-2024) ---- Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Police Forces of Syria (2024-) ---- Police Forces of Syria (2024-) ---- Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Rioters (Syria) ---- Unidentified Armed Group (Syria) ---- Police Forces of Syria (2024-) ---- Unidentified Armed Group (Syria)</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Military Forces of Iran (1989-) Islamic Revolutionary Guard Corps ---- Military Forces of the United States (2021-2025)</t>
+          <t>Students (Syria)</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Civilians (Syria) ---- Civilians (Syria) ---- QSD: Syrian Democratic Forces ---- Militia (Pro-Iran) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Students (Syria) ---- Students (Syria) ---- Teachers (Syria)</t>
+          <t>Prisoners (Syria); Students (Syria) ---- Students (Syria) ---- Teachers (Syria); Women (Syria) ---- Teachers (Syria) ---- Alawite Muslim Group (Syria); Former QDW: National Defence Forces; Students (Syria) ---- Alawite Muslim Group (Syria) ---- Students (Syria) ---- Students (Syria) ---- Alawite Muslim Group (Syria) ---- Teachers (Syria) ---- Druze Group (Syria); Students (Syria) ---- Alawite Muslim Group (Syria); Teachers (Syria) ---- Teachers (Syria) ---- Alawite Muslim Group (Syria); Students (Syria)</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>On 27 March 2024, IRGC detained three university students while they were taking photos of their building which was destroyed by airstrikes two days earlier in Deir-ez-Zor - Al-Qosor city in Deir ez Zor governorate. ---- On 31 March 2024, a Syrian police patrol, accompanied by security members from the IRGC, arrested 11 civilians, including university students, in the city of Deir-ez-Zor on allegations of photographing military positions. ---- Movement of forces: On 16 June 2024, QSD forces evacuated a military base at Al Jarsiya School in the town of Shiheil in the countryside of Deir ez Zor. ---- On 22 October 2024, an unidentified armed group targeted an educational institute in the town of Basira in the countryside of Deir ez Zor with a grenade. There were no casualties. ---- On 22 October 2024, Tribal and Clan Forces shelled a QSD military post inside a school in the village Hejneh in the countryside of Deir ez Zor with artillery, wounding two QSD members. There were no fatalities. ---- On 29 October 2024, US warplanes, operating under the Global Coalition, conducted an airstrike targeting a school held by pro-Iran militia in the village of Mathlum in the countryside of Deir ez Zor. casualties unknown. ---- On 22 January 2025, QSD forces launched a security operation and raided houses in Al Shanan, Thiban and Shiheil towns in Deir ez Zor countryside, and detained eight people including teachers and people with special needs for unknown reasons. The raids also included destroying contents of the houses and intimidation of women and children. ---- On 6 February 2025, QSD forces detained a man who works in an education institution in Maamel - 7 KM area in Deir ez Zor countryside for unknown reasons.</t>
+          <t>Around 5 February 2024 (month of), a student died under torture after being in detention since 2014 in one of the regime prisons in Homs, coded to Homs - Central Prison. The student hailed from Madiq Castle. 1 fatality. ---- On 9 March 2024, Syrian regime police detained a 9-year-old child from his school in the village of Marj al Qata in the countryside of Homs for distorting the picture of Bashar Al Assad by drawing on it in his textbook. Additionally, the school principal physically assaulted the child for doing so. ---- On 20 January 2025, an unidentified armed group kidnapped a woman in the city of Homs for unknown reasons. The abductee is an Assistant Professor at the University of Homs. ---- On 5 March 2025, a man's body with gunshot marks was found in Al-Waer neighborhood in Homs - Al-Waer city, killed by unknown gunmen pretending to be police forces after they kidnapped him the previous day. The man was a PE teacher. 1 fatality. ---- On 20 March 2025, unknown gunmen raided a house in Al Iddikhar neighborhood in Homs city, killing a 50-year-old man and his three sons, all members of the Alawite sect. The father had previously worked in construction in Algeria before returning to Syria. His sons included a 22-year-old former QDW member and two 19-year-old high school students. 4 fatalities. ---- On 2 April 2025, an unknown gunman on a motorbike threw a hand grenade at an Alawite family near a school in Homs - Karm al-Louz neighborhood in Homs city, killing a child, and injuring four people; a man, his wife, and their two children. 1 fatality. ---- On 25 April 2025, police forces raided a university student's house in Homs - Karm al-Louz neighborhood in Homs city, and arrested him for unknown reasons. On the same day, they raided a driver's house in the same neighborhood and arrested him for unknown reasons. The student's body was found later in Al Nahda hospital killed by presumably police forces, and the driver's body was also found in Al Waleed hospital killed by presumably police forces as well. 2 fatalities. ---- On 25 April 2025, three masked police members raided a university student's house in Homs - Nuzha neighborhood in Homs city, and arrested him for unknown reasons. They also threatened to kill his sick mother if anyone tries to go out to the balcony. The student's body was found later in a hospital killed by presumably police forces. In another incident police forces detained another man from his house in the same neighborhood, and his body was also found later near his house. 2 fatalities. ---- On 25 April 2025, residents found the body of a 58-year-old man from the Alawite sect near a School in Homs - Karm al-Zeitoun neighborhood of Homs city. The victim, who owned a grocery store in the same neighborhood, had been abducted earlier that day by unidentified gunmen from in front of his home. 1 fatality. ---- Around 26 April 2025 (as reported), the body of a teacher was found at Al-Basel Hospital in Homs city, killed by an unidentified armed group for unknown reasons. He had been reported missing two days earlier while on his way home in Wadi al-Thahab neighbourhood. 1 fatality. ---- On 28 April 2025, students at the dormitory of Homs University in Homs city stormed several rooms belonging to students from As-Sweida province, wounding one student with a gunshot amid sectarian chants. The incident occurred after a voice recording circulated among locals, allegedly featuring a Druze military commander from As-Sweida cursing the Prophet, which sparked widespread outrage. Police forces intervened to disperse the students and restore order. ---- On 3 May 2025, an unidentified armed group shot and killed a woman and wounded her husband and two children in Homs - Wadi al-Thahab neighborhood in Homs city for unknown reasons. Both victims were Alawite and the woman was a teacher. 1 fatality. ---- On 5 May 2025, Syrian police members arrested an Al Baath University professor at his home in Homs - Karm al-Zeitoun neighborhood in the city of Homs for unknown reasons. ---- Around 12 July 2025 (week of), an unidentified armed group shot and wounded a university student from Alawite community in Homs - Karm al-Louz neighborhood of Homs city. He succumbed to his injuries on 26 July. 1 fatality.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>2024-03-27 ---- 2024-03-31 ---- 2024-06-16 ---- 2024-10-22 ---- 2024-10-22 ---- 2024-10-29 ---- 2025-01-22 ---- 2025-02-06</t>
+          <t>2024-02-05 ---- 2024-03-09 ---- 2025-01-20 ---- 2025-03-05 ---- 2025-03-20 ---- 2025-04-02 ---- 2025-04-25 ---- 2025-04-25 ---- 2025-04-25 ---- 2025-04-26 ---- 2025-04-28 ---- 2025-05-03 ---- 2025-05-05 ---- 2025-07-12</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Deir ez Zor</t>
+          <t>Homs</t>
         </is>
       </c>
       <c r="AQ15" t="n">
@@ -2859,158 +2444,92 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SY0903</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>2024-10-22 ---- 2024-01-18</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>October 2024: An educational facility was attacked with a grenade by an unidentified armed group. ---- January 2024: Local gunmen attacked checkpoints near a school amidst artillery shelling by Iran-backed militias.</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building  ---- Education Building </t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>NSA ---- NSA</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Unidentified Armed Actor ---- Unidentified Armed Actor</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Hand Grenade ---- Firearms</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>School: No Further Details ---- School: No Further Details</t>
-        </is>
-      </c>
+          <t>SY0402</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Deir ez Zor</t>
+          <t>Homs</t>
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>SY09</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Violence against civilians ---- Battles ---- Explosions/Remote violence ---- Battles ---- Explosions/Remote violence ---- Battles ---- Strategic developments ---- Violence against civilians ---- Violence against civilians</t>
+          <t>Violence against civilians</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Attack ---- Change to group/activity ---- Change to group/activity ---- Change to group/activity ---- Change to group/activity ---- Change to group/activity ---- Attack ---- Armed clash ---- Shelling/artillery/missile attack ---- Armed clash ---- Shelling/artillery/missile attack ---- Armed clash ---- Headquarters or base established ---- Abduction/forced disappearance ---- Abduction/forced disappearance</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>Islamic State in Iraq and the Levant (ISIL) ---- Militia (Pro-Iran) ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces ---- Military Forces of Syria (2000-2024) ---- QSD: Syrian Democratic Forces ---- Unidentified Armed Group (Syria) ---- QSD: Syrian Democratic Forces ---- Military Forces of Syria (2000-2024) ---- Fatemiyoun Brigade ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Militia (Pro-Iran)</t>
-        </is>
-      </c>
+          <t>Unidentified Armed Group (Syria)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Civilians (Syria) ---- Civilians (Syria) ---- QSD: Syrian Democratic Forces ---- Military Forces of Syria (2000-2024) ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces ---- Civilians (Syria) ---- Civilians (Syria)</t>
+          <t>Civilians (Syria)</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Teachers (Syria) ---- Students (Syria) ---- Civilians (Syria); Students (Syria) ---- Teachers (Syria) ---- Teachers (Syria)</t>
+          <t>Shiite Muslim Group (Syria); Teachers (Syria)</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>On 26 January 2024, IS members shot and killed a teacher in Al-Hawayij town in Deir ez Zor countryside. 1 fatality. ---- Movement of forces: On 28 January 2024, pro-Iran militias evacuated their bases in In Al-Tammu neighborhood and near Al Hasan school as well as the farms in the town of Al Mayadin in the countryside of Deir ez Zor. ---- Movement of forces: On 30 January 2024, QSD forces evacuated a base that was previously a school in Abu Hardoub in the countryside of Deir ez Zor. ---- Movement of forces: On 30 January 2024, QSD forces evacuated a base that was previously a school in Eastern Jurdi in the countryside of Deir ez Zor. ---- Movement of forces: On 30 January 2024, QSD forces evacuated a base that was previously a school in Al Mawh in Thiban in the countryside of Deir ez Zor. ---- Movement of forces: On 30 January 2024, QSD forces evacuated a base that was previously a school in Al-Diaf in the countryside of Deir ez Zor. ---- On 14 February 2024, QSD members shot and killed a child in a school in Al Shanan town in Deir ez Zor countryside. 1 fatality. ---- On 24 February 2024, armed clashes took place between regime members and QSD fighters by the Euphrates river between Sweidan Jazira and Sweidan Shamiyeh in rural Deir ez Zor, causing material damage to civilian residences, a school and a water station. Casualties unknown. ---- On 28 February 2024, QSD shelled regime forces positions in Al Mayadin town in Deir ez Zor countryside with mortar shells, killing a civilian who is a high school student and injuring two others. 1 fatality. ---- On 13 April 2024, unidentified gunmen targeted a QSD-affiliated position in a school near Al Shanan village in rural eastern Deir ez Zor, triggering QSD fighters to fire gunshots randomly. Casualties unknown. ---- On 28 September 2024, QSD fighters shelled around Al Mayadin - City Bridge in rural Deir ez Zor and near a school in Al Mayadin city and its outskirts with mortars. Casualties unknown. ---- On 28 September 2024, armed clashes took place between regime members and pro-Iranian militia stationed in Al Mayadin city against QSD fighters on the opposite bank of the Euphrates river with light and medium weapons in conjunction with QSD fighters shelling near a school in Al Mayadin city in rural Deir ez Zor with mortars without causing any casualties. ---- On 29 September 2024, Fatemiyoun Brigade established a new military base in a school in the village of Quriyeh in the countryside of Deir ez Zor. ---- On 22 January 2025, QSD forces launched a security operation and raided houses in Al Shanan, Thiban and Shiheil towns in Deir ez Zor countryside, and detained eight people including teachers and people with special needs for unknown reasons. The raids also included destroying contents of the houses and intimidation of women and children. ---- On 22 January 2025, QSD forces launched a security operation and raided houses in Al Shanan, Thiban and Shiheil towns in Deir ez Zor countryside, and detained eight people including teachers and people with special needs for unknown reasons. The raids also included destroying contents of the houses and intimidation of women and children.</t>
+          <t>On 20 April 2025, an unidentified armed group shot and killed a Shiite civilian in the village of Diyabiya in the countryside of Homs, for unknown reasons. The victim was a school principal. 1 fatality.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>2024-01-26 ---- 2024-01-28 ---- 2024-01-30 ---- 2024-01-30 ---- 2024-01-30 ---- 2024-01-30 ---- 2024-02-14 ---- 2024-02-24 ---- 2024-02-28 ---- 2024-04-13 ---- 2024-09-28 ---- 2024-09-28 ---- 2024-09-29 ---- 2025-01-22 ---- 2025-01-22</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>Al Mayadin</t>
+          <t>Al Qusayr</t>
         </is>
       </c>
       <c r="AQ16" t="n">
@@ -3020,158 +2539,92 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SY1000</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>September 2024: The body of a educator was found with gunshot injuries.</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Private Travel</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Firearms</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
+          <t>SY0404</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Tartous</t>
+          <t>Homs</t>
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>SY10</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Protests ---- Violence against civilians</t>
+          <t>Explosions/Remote violence</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Attack ---- Peaceful protest ---- Attack</t>
+          <t>Remote explosive/landmine/IED</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Unidentified Armed Group (Syria)</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Teachers (Syria)</t>
-        </is>
-      </c>
+          <t>Unidentified Armed Group (Syria)</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Civilians (Syria) ---- Civilians (Syria)</t>
+          <t>Civilians (Syria)</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Teachers (Syria) ---- Alawite Muslim Group (Syria); Students (Syria)</t>
+          <t>Former QDW: National Defence Forces; Government of Syria (2000-2024)</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>Around 21 September 2024 (week of), the body of a young man was found with signs of gunshot wounds along an agricultural road east of Mi'yar Shaker in rural Tartous, killed by unidentified gunmen for unknown reasons. The victim is a teacher in his 40s. 1 fatality. ---- On 27 January 2025, dozens of teachers staged a protest in the city of Tartous, opposing the caretaker government's decision to revoke their right to choose their workplace and to mandate their return to their original areas. ---- On 30 March 2025, Syrian police members shot and killed a seventeen-year-old child who is an Alawite high school student near the Karto village junction near the village of Kareemeh in the countryside of Tartous after he attempted to escape a checkpoint Syrian police members had set-up along the road. The victim is from Shass village. 1 fatality.</t>
+          <t>On 19 November 2024, an IED planted inside a school bus by an unidentified armed group detonated in the village of Tesnine in in the countryside of Homs, killing the head of Kafr Nan village municipality, who was also a former QDW commander. 1 fatality.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>2024-09-21 ---- 2025-01-27 ---- 2025-03-30</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>Tartous</t>
+          <t>Ar Rastan</t>
         </is>
       </c>
       <c r="AQ17" t="n">
@@ -3181,158 +2634,88 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SY1101</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>2025-02-01 ---- 2024-11-02</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">February 2025: An educational facility was hit by Turkish forces, who conducted four airstrikes on SDF positions. ---- November 2024: Five educators were arrested by the SDF after they resigned in protest against an SDF-imposed curriculum. </t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Education Building  ---- Unspecified Location</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Foreign Forces - Military ---- NSA</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Armed Forces of Turkey ---- Syrian Democratic Forces</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Aerial Bomb: Plane ---- Firearms</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>University ---- Not Applicable</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>NoInformation</t>
-        </is>
-      </c>
+          <t>SY0405</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ar Raqqa</t>
+          <t>Homs</t>
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>SY11</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Strategic developments ---- Strategic developments ---- Violence against civilians ---- Violence against civilians ---- Riots ---- Battles ---- Violence against civilians ---- Violence against civilians</t>
+          <t>Battles</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Disrupted weapons use ---- Arrests ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Violent demonstration ---- Armed clash ---- Abduction/forced disappearance ---- Abduction/forced disappearance</t>
+          <t>Armed clash</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>Police Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces ---- Rioters (Syria) ---- Unidentified Armed Group (Syria) ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces</t>
+          <t>Islamic State in Iraq and the Levant (ISIL)</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Unidentified Armed Group (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- QSD: Syrian Democratic Forces ---- Civilians (Syria) ---- Civilians (Syria)</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Students (Syria) ---- Teachers (Syria); Women (Syria) ---- Women (Syria); Teachers (Syria) ---- Students (Syria) ---- Teachers (Syria)</t>
-        </is>
-      </c>
+          <t>Military Forces of Syria (2000-2024)</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>Defusal: On 15 July 2024, Syrian police forces dismantled an IED planted by an unidentified armed group near a polling center inside a school in the town of Maadan in the countryside of Ar Raqqa. ---- On 6 August 2024, Syrian regime forces arrested two university students at Hweijet Shnan checkpoint in the countryside of Ar Raqqa for unknown reasons. ---- On 27 October 2024, QSD forces detained four female teachers in the city of Ar-Raqqa for refusing to teach the new curriculum imposed by the group. ---- On 2 November 2024, QSD fighters detained five female teachers in Ar-Raqqa city after the teachers resigned from their positions in condemnation of a QSD-imposed teaching curricula which includes 'false historical and geographical information'. During the past few days, the teachers participated in a strike for the same reason. ---- On 2 November 2024, residents held a demonstration in the city of Ar-Raqqa - Al-Mashlab neighborhood and blocked a main road in the neighborhood with burning tires condemning QSD's detainment of five female teachers following their resignation denouncing the QSD-affiliated school curricula imposed on schools in the area. ---- On 12 February 2025, unknown gunmen attacked a QSD military point near Al Farabi school in Al Rmeleh neighborhood in Ar-Raqqa city with machine guns. Casualties unknown. ---- On 17 March 2025, QSD forces detained a university student in the city of Ar-Raqqa for raising the Syrian flag and celebrating the 14th anniversary of the Syrian revolution. ---- On 26 April 2025, QSD forces detained the head of the exam centre, the head of the educational complex, and a teacher in the village of Sabka in the countryside of Ar-Raqqa. They also seized all equipment from the centre and relocated it to the city of Ar-Raqqa for unknown reasons.</t>
+          <t>On 28 May 2024, IS members attacked a military post held by Syrian regime forces near a driving school in the area of Tadmor in the countryside of Homs, killing one regime soldier. 1 fatality.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>2024-07-15 ---- 2024-08-06 ---- 2024-10-27 ---- 2024-11-02 ---- 2024-11-02 ---- 2025-02-12 ---- 2025-03-17 ---- 2025-04-26</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>Ar Raqqa</t>
+          <t>Tadmor</t>
         </is>
       </c>
       <c r="AQ18" t="n">
@@ -3342,128 +2725,66 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SY1200</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>2024-09-22 ---- 2024-08-23</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">September 2024: An unspecified number of schools were damaged when Israeli forces shot down a suicide drone launched from Iraq by the Islamic Resistance in Iraq as it passed through Syria toward the Golan Heights. The interception occurred in the village. ---- August 2024: The body of a man who works in a school was found near a school campus, shot and killed by unidentified perpetrators. </t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building  ---- Education Building </t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Multiple ---- No Information</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Islamic Resistance in Iraq, Israeli Defence Forces ---- No Information</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Aerial Bomb: Drone, Firearms ---- Firearms</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>School: No Further Details ---- School: No Further Details</t>
-        </is>
-      </c>
+          <t>SY0501</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Dara</t>
+          <t>Hama</t>
         </is>
       </c>
       <c r="AD19" t="n">
         <v>4</v>
       </c>
       <c r="AE19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>SY12</t>
+          <t>SY05</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Violence against civilians ---- Explosions/Remote violence ---- Violence against civilians ---- Battles ---- Protests ---- Violence against civilians ---- Strategic developments</t>
+          <t>Explosions/Remote violence ---- Violence against civilians ---- Protests ---- Strategic developments ---- Violence against civilians</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Remote explosive/landmine/IED ---- Remote explosive/landmine/IED ---- Attack ---- Air/drone strike ---- Abduction/forced disappearance ---- Non-state actor overtakes territory ---- Peaceful protest ---- Abduction/forced disappearance ---- Arrests</t>
+          <t>Air/drone strike ---- Attack ---- Peaceful protest ---- Other ---- Attack</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Islamic Resistance in Iraq ---- Unidentified Armed Group (Syria) ---- Southern Operations Room ---- Protesters (Syria) ---- Military Forces of Israel (2022-) ---- Police Forces of Syria (2024-)</t>
+          <t>Military Forces of Syria (2000-2024) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Military Forces of Syria (2000-2024) ---- Police Forces of Syria (2024-)</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -3473,27 +2794,27 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Military Forces of Syria (2000-2024) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Labor Group (Syria); Teachers (Syria) ---- Students (Syria) ---- Farmers (Syria); Students (Syria) ---- Students (Syria)</t>
+          <t>Students (Syria); Teachers (Syria) ---- Students (Syria)</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>On 17 February 2024, an IED previously planted by unidentified gunmen at a fuel depot near a school and al Saraya building in Dar'a city detonated, causing material damage without causing any casualties. ---- On 8 May 2024, an IED planted by unknown gunmen exploded in Al Mahatta area in Dar'a city, killing a civilian who is a teacher and works as a taxi driver. 1 fatality. ---- Around 23 August 2024 (week of), the body of a man who works in a school was found near Al Manar school on Abtaa-Sheikh Miskine road in Dara countryside, shot and killed by unknown gunmen. 1 fatality. ---- Interception: On 22 September 2024, Israeli forces shot down a suicide drone launched from Iraq by the Islamic Resistance in Iraq as it passed through Syria toward the Golan Heights. The interception occurred in Jomleh village in the Dara countryside, causing material damage to local schools and resulting in minor injuries to a woman from shattered glass. ---- On 19 November 2024, an unidentified armed group kidnapped a university student on the road to Abtaa in the countryside of Dara for unknown reasons. The student had previously been blackmailed for money. ---- On 6 December 2024, opposition factions operating under the Southern Operations Room clashed with regime fighters on the outskirts of Da'el and took control of a school and a checkpoint along the Da'el - Atman road and several checkpoints between Da'el and Tafas in rural Dara in conjunction with Syrian regime fighters shelling Da'el city with artillery, killing two young men during clashes along the Da'el - Tafas road and capturing two regime fighters. 2 fatalities. ---- On 25 February 2025, students from Nafeaa in rural Dara held a protest condemning a recent Israeli statement calling for the disarmament of southern Syria and condemning projects that threaten Syria's unity. ---- On 28 March 2025, Israeli forces detained three people two of whom are university students while working in a farmland in Yarmouk Basin in Dara countryside. ---- On 8 August 2025, police forces arrested a university student from As Sweida province at Busra Esh-Sham checkpoint in Dara countryside for unknown reasons.</t>
+          <t>On 6 December 2024, regime forces targeted two schools in the southern al Malab neighborhood and a residential neighborhood south of the stadium in Hama city with airstrikes, a cruise missile and rocket shelling, killing at least four civilians including a father and his three children and injuring six other civilians including a women and two of her children. 4 fatalities coded. ---- On 12 February 2025, unknown gunmen shot and injured a young man from Suran near a driving school in rural Suran in northern Hama countryside. There were no fatalities. ---- On 7 April 2025, university students staged a protest at the National Private University campus in Hama city, against the Israeli attacks on the Gaza Strip and in support of the Palestinian people. ---- Mass grave: On 15 April 2025, a mass grave was discovered near al-Hukamaa School on the Muhradah road in Hama city, containing the remains of three individuals who had been missing for about 11 years. The site was near a large Syrian regime military checkpoint operated by Iranian militias. The victims were detained and executed there by former regiem forces. 3 fatalities. ---- On 30 April 2025, police members physically assaulted three young men one of whom is Christian, and shaved their heads, because they were sitting with girls in the university in Hama city. The students filed a complaint against the police members, whom were brought for investigation, and were forced to apologize to the students.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>2024-02-17 ---- 2024-05-08 ---- 2024-08-23 ---- 2024-09-22 ---- 2024-11-19 ---- 2024-12-06 ---- 2025-02-25 ---- 2025-03-28 ---- 2025-08-08</t>
+          <t>2024-12-06 ---- 2025-02-12 ---- 2025-04-07 ---- 2025-04-15 ---- 2025-04-30</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>Dara</t>
+          <t>Hama</t>
         </is>
       </c>
       <c r="AQ19" t="n">
@@ -3503,124 +2824,61 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SY1203</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">September 2024: A school was damaged when an unidentified armed group detonated a grenade nearby._x000D_
-</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>NSA</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Unidentified Armed Actor</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Hand Grenade</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>School: No Further Details</t>
-        </is>
-      </c>
+          <t>SY0502</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Dara</t>
+          <t>Hama</t>
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>SY12</t>
+          <t>SY05</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence</t>
+          <t>Violence against civilians</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Grenade</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3629,21 +2887,29 @@
         </is>
       </c>
       <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Farmers (Syria); Former Military Forces of Syria (2024-); Labor Group (Syria); Teachers (Syria); Alawite Muslim Group (Syria)</t>
+        </is>
+      </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>On 8 September 2024, an unidentified armed group detonated a grenade near a school in the town of Jasim in the countryside of Dara, causing only material damages. There were no casualties.</t>
+          <t>On 10 March 2025, unidentified armed groups traveling in several vehicles stormed Al Aziziyeh village in rural Hama and abducted eight Alawite men after raiding their homes. Over the next several days, five of the victim's bodies were found including a farmer who ran a workshop was found in Tamanah on 10 March, a teacher who is a former regime-affiliated 4th division member was found near Tamanah on 11 March, a third and fourth victims' bodies were found near al Rasif village on 12 March, and the fifth victim's body was found in agricultural land in the vicinity of Al Aziziyeh on 17 March , killed by their abductors. The whereabouts of three of the remaining abducted victims remains unknown. 5 fatalities.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>Izra</t>
+          <t>As Suqaylabiyah</t>
         </is>
       </c>
       <c r="AQ20" t="n">
@@ -3653,157 +2919,2981 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SY1400</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>April 2025: An education facility was raided by Israeli military forces during school hours.</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Foreign Forces - Military</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Israeli Defence Forces</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Firearms</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>School: No Further Details</t>
-        </is>
-      </c>
+          <t>SY0503</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Quneitra</t>
+          <t>Hama</t>
         </is>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>SY14</t>
+          <t>SY05</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Violence against civilians ---- Strategic developments</t>
+          <t>Battles</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance ---- Looting/property destruction ---- Change to group/activity ---- Change to group/activity ---- Abduction/forced disappearance ---- Looting/property destruction</t>
+          <t>Non-state actor overtakes territory</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-)</t>
+          <t>Military Operations Command</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr">
         <is>
+          <t>Military Forces of Syria (2000-2024)</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>On 3 December 2024, Military Operations Command forces took control of Hama Armored Vehicles School in the countryside of Hama following clashes with regime forces as part of the 'Deter of Aggression' operation. During the clashes, Military Operations Command forces conducted Shahin drone strikes targeting Syrian regime military positions in the town. Casualties unknown.</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>As Salamiyeh</t>
+        </is>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SY0600</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">August 2024: A school was hit and damaged by shelling by Syria regime forces. The school was out of service due to the displacement of the village's residents. </t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Syrian Armed Forces</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Shelling</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Lattakia</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>SY06</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Strategic developments ---- Violence against civilians ---- Protests ---- Violence against civilians ---- Battles</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Air/drone strike ---- Shelling/artillery/missile attack ---- Other ---- Attack ---- Peaceful protest ---- Attack ---- Armed clash</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Civilians (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Police Forces of Syria (2024-) ---- Anti-Military Operations Command Militia (Syria)</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Turkmen Communal Group (Syria) ---- Teachers (Syria) ---- Ministry of Defense of the Syrian Interim Government</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Police Forces of Syria (2024-)</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Teachers (Syria) ---- Students (Syria) ---- Labor Group (Syria)</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>On 17 March 2024, Syrian regime forces conducted a suicide drone attack near a school in the village of Yamdiyeh in the countryside of Lattakia. There were no casualties. ---- On 3 August 2024, regime fighters shelled a school in Nawwara-Klz (Klz) village in rural Lattakia, causing material damage without causing any casualties. The school was out of service due to the displacement of the village's residents. ---- Other: On 21 December 2024, local residents who are majority Turkmen group members expelled non-Turkmen teachers and the school's principal from a school in Al Issawiyya in rural Lattakia over sectarian affiliations. Teachers accused unspecified groups who are loyal to Turkey of pressuring residents to expel non-Turkmen teachers. The new regime has not taken any action in response. ---- On 26 December 2024, unknown gunmen shot and killed a student in the faculty of medicine in Lattakia city. 1 fatality. ---- On 23 January 2025, tens of teachers staged a protest in front of the education directorate building in Lattakia city, against the decision of ending the duty location and returning them to their areas of origin. ---- On 4 March 2025, Syrian police members conducted a security operation in Lattakia - Da'tor neighborhood and several other neighborhoods in Lattakia city targeting former regime remnants, during which they shot several civilians, killing four of them including two school guards and arresting several wanted individuals. On the same day, the Ministry of Defense of the Syrian Interim Government deployed vehicles equipped with machine guns to the vicinity of the neighborhood in search of drug dealers, former regime remnants and individuals who escaped from prisons. 4 fatalities. ---- On 6 March 2025, an Anti-Military Operations Command militia attacked the headquarters of the General Security Forces (police forces) in Lattakia - Teshreen Suburb neighborhood in Lattakia city. One of the attackers was killed, and three others were arrested. During the clashes, one university student was killed. 2 fatalities.</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>2024-03-17 ---- 2024-08-03 ---- 2024-12-21 ---- 2024-12-26 ---- 2025-01-23 ---- 2025-03-04 ---- 2025-03-06</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>Lattakia</t>
+        </is>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SY0602</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lattakia</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>SY06</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Police Forces of Syria (2024-)</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>On 5 June 2025, police forces raided Beit Ana town in Lattakia countryside, and burned tens of houses, a school and other facilities, they also killed 3 young men two of whom with special needs. 3 fatalities.</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>Jablah</t>
+        </is>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SY0604</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Lattakia</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>SY06</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Strategic developments ---- Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Arrests ---- Arrests ---- Remote explosive/landmine/IED</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Police Forces of Syria (2024-) ---- Police Forces of Syria (2024-) ---- Unidentified Armed Group (Syria)</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Students (Syria) ---- Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>On 21 April 2025, Syrian police forces arrested eight individuals, including a high-school student, in Bayit Atiqa in the countryside of Al-Qardaha in Lattakia province, for unknown reasons. ---- On 13 May 2025, Syrian police members arrested two young men in rural Al-Qardaha in Lattakia's countryside. While one young man's arrest is suspected to be linked to an unspecified video found on his phone, the second young man who is a university student was arrested for unknown reasons. ---- On 14 May 2025, an unexploded shell from previous clashes by unknown gunmen exploded behind a school in Bhamra town in Lattakia countryside, killing 1 child, and injuring five others. 1 fatality.</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>2025-04-21 ---- 2025-05-13 ---- 2025-05-14</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>Al Qardaha</t>
+        </is>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SY0700</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2024-09-15 ---- 2024-08-21 ---- 2024-03-19 ---- 2024-03-19 ---- 2024-01-07 ---- 2024-01-05</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>September 2024: A school was damaged by Syrian forces shelling on the area. A child and a young man were injured. ---- August 2024: A school was hit when Syrian regime forces shelled the area.  ---- March 2024: An elementary school was hit by Syrian regime forces rockets, partially destroying it. ---- March 2024: An elementary school and homes were hit by Syrian regime forces rockets. ---- January 2024: Syrian forces targeted a school-turned-shelter with incendiary weapons. One civilian sustained burns, whilst three others got wounded by missile shrapnel. ---- January 2024: Government forces attacked a school, injuring a child, who later died of their injuries.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Other ---- Other ---- Other ---- Other ---- Other ---- Other</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Shelling ---- Shelling ---- Rocket ---- Rocket ---- Missile ---- Artillery</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>School: No Further Details ---- School: No Further Details ---- Primary School ---- Primary School ---- School: No Further Details ---- School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Idleb</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>SY07</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Explosions/Remote violence ---- Protests ---- Protests ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Protests ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Shelling/artillery/missile attack ---- Peaceful protest ---- Peaceful protest ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Peaceful protest ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Military Forces of Syria (2000-2024) ---- Protesters (Syria) ---- Protesters (Syria) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Protesters (Syria) ---- Military Forces of Russia (2000-) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Russia (2000-) ---- Protesters (Syria) ---- Protesters (Syria)</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Teachers (Syria) ---- Students (Syria) ---- Students (Syria) ---- Teachers (Syria) ---- Students (Syria) ---- Teachers (Syria) ---- Teachers (Syria) ---- Students (Syria) ---- Students (Syria) ---- Teachers (Syria) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Teachers (Syria) ---- Teachers (Syria)</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Refugees/IDPs (Syria); Teachers (Syria) ---- Students (Syria); Teachers (Syria) ---- Teachers (Syria); Students (Syria) ---- Students (Syria); Teachers (Syria) ---- Health Workers (Syria); Refugees/IDPs (Syria); Students (Syria); Teachers (Syria)</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>On 3 January 2024, regime forces shelled a school in Afes town in Idleb countryside with artillery. A child died on 5th January from wounds sustained. 1 fatality. ---- On 19 March 2024, Syrian regime forces shelled a school in the village of Ketyan in the countryside of Idleb with rockets, causing only material damages. There were no casualties. ---- On 19 March 2024, Syrian regime forces shelled a school in the village of Toum in the countryside of Idleb with rockets, causing only material damages. There were no casualties. ---- On 1 April 2024, Syrian regime forces shelled a school in the town of Sarmin in the countryside of Idleb with rockets, killing a woman and a child, and wounding 9 civilians. 2 fatalities. ---- On 20 April 2024, tens of teachers organized a protest outside the directorate of education in the city of Idleb against their dismissals and calling for the decision to be overturned. ---- On 1 May 2024, students of the University of Idleb staged a protest in the city of Idleb, denouncing the Israeli assault on Gaza strip and in support of Palestinians. ---- On 4 May 2024, university students held a protest in front of the HTS-affiliated Syrian Salvation Government Prime Minister's office in Idleb city against the SSG's acceptance of graduates from regime-controlled areas into SSG institutions. ---- On 9 May 2024, teachers staged a protest in front of the Syrian Salvation Government building in the city of Idleb, demanding a rise in their salaries. ---- On 14 May 2024, twenty students who graduated from universities in Syrian regime-held areas staged a protest in front of the Syrian Salvation Government building in the city of Idleb, denouncing the decision to withdraw recognition of their diplomas. ---- On 16 May 2024, teachers organized a protest in front of Al Inkaz government building in Idleb city, demanding to improve living conditions, and to raise their salaries. ---- On 11 August 2024, teachers staged a protest in the city of Idleb against the decision to remove the French language from schools' curriculum. ---- On 21 August 2024, regime forces shelled Sarmin town including a school inside the town in Idleb countryside with heavy artillery. Casualties unknown. ---- On 31 August 2024, dozens of residents including students held a protest in front of Idleb University in Idleb city condemning the acceptance of students from regime-controlled areas in universities in northern Syria and their employment following their graduation. ---- On 4 September 2024, university students staged a protest in Idleb city, against appointing graduates of regime universities. ---- On 15 September 2024, Syrian regime forces shelled the town of Sarmin in the countryside of Idleb with artillery, wounding a child and a young man. Additionally, regime forces shelled a school in the town, causing material damage to the building. There were no fatalities. ---- On 16 November 2024, regime fighters shelled Teftnaz in rural Idleb with artillery, killing a displaced Quranic teacher from Saraqab and injuring three others. 1 fatality. ---- On 25 November 2024, teachers staged a protest against the Syrian Salvation Government in the city of Idleb, demanding a rise in their wages. ---- On 28 November 2024, Russian warplanes conducted airstrikes targeting the vicinity of Sarmin town in Idleb countryside in conjunction with regime fighters shelling a primary school in Sarmin city with rockets, injuring three civilians and causing material damage. There were no fatalities. ---- On 29 November 2024, Regime warplanes conducted airstrikes targeting two schools in Idleb city and its outskirts respectively and a nearby fuel station and water station in conjunction with regime fighters shelling the city with missiles, killing four civilians, wounding 19 others and causing material damage to the fuel station and a school. 4 fatalities. ---- On 1 December 2024, regime warplanes conducted several airstrikes throughout the day targeting several sites and facilities in Idleb city including three schools, a residential building in the outskirts of the city and near an ambulatory services center, killing fourteen civilians, including five children and a woman, wounding more than 59 others and causing material damage. 14 fatalities. ---- On 2 December 2024, Russian and regime warplanes carried out two airstrikes on a cluster of hospitals and health centers in the city of Idleb, and several airstrikes on a school, residential areas including Dawwar Shamma' and al Thawra neighborhoods as well as a refugee camp in Idleb city, killing twenty-one civilians including five women and eight children and wounding sixty-three other civilians including thirty children and twenty women. On 16 December, one individual died from injuries sustained. 22 fatalities. ---- On 25 February 2025, teachers held a protest in Idleb city calling to be reinstated to their teaching positions and payment of their suspended salaries after they were dismissed for participating in the Syrian revolution under the former regime. ---- On 5 July 2025, dozens of teachers staged a protest in the city of Idleb, denouncing a decision by the Minister of Education to reduce summer salaries from $150 to $90 per month.</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>2024-01-03 ---- 2024-03-19 ---- 2024-03-19 ---- 2024-04-01 ---- 2024-04-20 ---- 2024-05-01 ---- 2024-05-04 ---- 2024-05-09 ---- 2024-05-14 ---- 2024-05-16 ---- 2024-08-11 ---- 2024-08-21 ---- 2024-08-31 ---- 2024-09-04 ---- 2024-09-15 ---- 2024-11-16 ---- 2024-11-25 ---- 2024-11-28 ---- 2024-11-29 ---- 2024-12-01 ---- 2024-12-02 ---- 2025-02-25 ---- 2025-07-05</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>Idleb</t>
+        </is>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SY0702</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>February 2024: A school was damaged when Syrian regime forces shelled the area.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Syrian Armed Forces</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Shelling</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SY0703</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">June 2024: A educator was arrested by HTS personnel who raided his home over his participation in anti-HTS protests. He was taken to an undisclosed location. </t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tahrir al-Sham</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Fist and Foot</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>NoInformation</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Idleb</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>SY07</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Air/drone strike</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Global Coalition Against Daesh</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Islamic State in Iraq and the Levant (ISIL)</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Civilians (Syria); Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>On 15 January 2025, Global Coalition targeted a motorbike with two suspected ISIL members on Al Qal'a camp road northwest of Sarmada town in Idleb countryside with a drone, killing them both, and injuring a student who was near the location. The student died from his wounds on 17th. 3 fatalities.</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>Harim</t>
+        </is>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SY0705</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2024-11-29 ---- 2024-11-26 ---- 2024-11-26 ---- 2024-01-22 ---- 2024-01-22 ---- 2024-01-18 ---- 2024-01-08</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>November 2024: A school was hit by Syrian and Russian airstrikes. ---- November 2024: An educational facility was damaged by Syrian regime forces shelling, killing and injuring an unspecified number of people including children.  ---- November 2024: A school was damaged by Syrian regime forces shelling, killing and injuring an unspecified number of people including children.  ---- January 2024: Rocket fired by Syrian regime forces struck and partially destroyed the perimeter fence of a school. ---- January 2024: Rocket fired by Syrian regime forces rocket struck and damaged the perimeter fence of a school, whilst students were taking exams. ---- January 2024: Two rockets fired by Syrian regime forces directly hit a school, partially destroying the building and damaging furniture. ---- January 2024: Shell fired by Syrian regime forces hit and partially destroyed the perimeter fence of an elementary school, a few hours after students had gone home.</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Other ---- Other ---- Other ---- Other ---- Other ---- Other ---- Other</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Syrian or Russian Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces ---- Syrian Armed Forces</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aerial Bomb: Plane ---- Shelling ---- Shelling ---- Rocket ---- Rocket ---- Rocket ---- Shelling</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Secondary School ---- School: No Further Details ---- Primary School ---- Primary School</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Idleb</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>SY07</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Air/drone strike</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024)</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Students (Syria); Teachers (Syria) ---- Students (Syria); Teachers (Syria)</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>On 8 January 2024, regime forces shelled the village of Eblin in the countryside of Idleb with artillery, and a shell fell on a school fence partially damaging it. Casualties unknown. ---- On 18 January 2024, regime forces shelled Mseibin town hitting a school with two rockets in Idleb countryside with artillery and rockets, partially damaging the school. Casualties unknown. ---- On 22 January 2024, Syrian regime forces shelled the town of Ariha partially damaging a school fence in the countryside of Idleb with rockets, wounding five civilians, including two children. There were no fatalities. ---- On 21 February 2024, regime forces shelled Bara town in Idleb countryside with artillery, a shell fell near a school causing only material damage. There were no casualties. ---- On 26 November 2024, Syrian regime forces shelled an educational center and a school in the town of Ariha in the countryside of Idleb with artillery, killing three civilians including two children, and wounding fourteen others. 2 fatalities. ---- On 29 November 2024, regime warplanes targeted a school and nearby house on the southeastern outskirts of Ferkia village in rural Idleb, injuring seven civilians including six children and causing material damage. There were no fatalities.</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>2024-01-08 ---- 2024-01-18 ---- 2024-01-22 ---- 2024-02-21 ---- 2024-11-26 ---- 2024-11-29</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>Ariha</t>
+        </is>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SY0800</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2025-04-02 ---- 2024-12-12</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>April 2025: A student was abducted by PKK's YDG-H (Al Shabiba Al Thawria) members inside an educational facility. ---- December 2024: An education facility was destroyed by artillery fired by Turkish forces and Turkish-backed factions (JWS), operating under special operation forces.</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>NSA ---- Multiple</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kurdistan Workers' Party ---- Unidentified Armed Actor</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Firearms ---- Artillery</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Not Applicable ---- School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>NoInformation</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Al Hasakeh</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>SY08</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Violence against civilians ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Abduction/forced disappearance ---- Attack ---- Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>PKK: Kurdistan Workers Party ---- Unidentified Armed Group (Syria) ---- PKK: Kurdistan Workers Party</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>YDG-H: Patriotic Revolutionary Youth Movement ---- YDG-H: Patriotic Revolutionary Youth Movement</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Women (Syria) ---- Teachers (Syria) ---- Students (Syria); Women (Syria)</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>On 6 March 2024, PKK's YDG-H (Al Shabiba Al Thawria) members detained a sixteen year old girl in front of Adnan Al Maliki school in Tal Tamer town in Al Hasakeh countryside presumably for conscription. ---- On 26 January 2025, an unidentified armed group shot and killed teacher at Al-Hubat crossing south of Al-Hasakeh city, for unknown reasons. 1 fatality. ---- On 2 April 2025, PKK's YDG-H (Al Shabiba Al Thawria) members abducted a sixteen-year-old girl in That Al Nitaqen school in Al Nasirah neighborhood in Al-Hasakeh city for conscription.</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>2024-03-06 ---- 2025-01-26 ---- 2025-04-02</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>Al Hasakeh</t>
+        </is>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SY0802</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Al Hasakeh</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>SY08</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Violence against civilians ---- Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Air/drone strike ---- Abduction/forced disappearance ---- Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Military Forces of Turkey (2016-) ---- PKK: Kurdistan Workers Party ---- Protesters (Syria) ---- Protesters (Syria)</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>YDG-H: Patriotic Revolutionary Youth Movement ---- Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>On 14 January 2024, Turkish forces conducted a drone strike targeting a former driving school in the village of Girebawi in the countryside of Al Hasakeh. Casualties unknown. ---- On 9 May 2024, PKK's YDG-H (Al Shabiba Al Thawria) members detained a seventeen-year-old boy while he was leaving school in Amuda town in Al Hasakeh countryside for unknown reasons. ---- On 27 April 2025, dozens of parents of middle and high school students staged a protest outside the UNICEF headquarters in the city of Quamishli in the countryside of Al Hasakeh, to protest the ongoing denial of their children's right to sit for exams in Al Hasakeh Governorate. ---- On 29 April 2025, dozens of students and their families held a protest in front of a UN headquarters in Quamishli city in rural Al Hasakeh condemning an ongoing dispute between the Syrian government and DFNS over primary and secondary school examinations to be held in QSD-controlled areas.</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>2024-01-14 ---- 2024-05-09 ---- 2025-04-27 ---- 2025-04-29</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>Quamishli</t>
+        </is>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SY0804</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Al Hasakeh</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>SY08</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Attack ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>National Police Forces ---- Operation Peace Spring ---- Operation Peace Spring ---- FaR: Al Rahman Corps</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>JWS: Syrian National Army; Military Forces of Turkey (2016-) ---- JWS: Syrian National Army; Military Forces of Turkey (2016-)</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Civilians (Syria) ---- QSD: Syrian Democratic Forces ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Teachers (Syria)</t>
+        </is>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>On 4 April 2024, National Police Forces members beat two teachers in a bank in Ras al-Ain town in Al Hasakeh countryside, for criticizing delayed salaries and the small number of students in the school. ---- On 21 December 2024, Turkish and JWS fighters operating under Operation Peace Spring shelled QSD positions in the vicinity of Abu Rasin in rural Al Hasakeh with artillery in conjunction with targeting a school and fuel station in Abur Rasin town with artillery. Casualties unknown. ---- On 22 December 2024, Turkish forces and JWS, operating under OPS, shelled the village of Abu Rasin in the countryside of Al Hasakeh with artillery, targeting a gas station and a school. Casualties unknown. ---- On 6 January 2025, Al Rahman Corps fighters detained four civilians for writing pro-QSD slogans on the wall of a school in Ras al-Ain in rural Al Hasakeh.</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>2024-04-04 ---- 2024-12-21 ---- 2024-12-22 ---- 2025-01-06</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>Ras Al Ain</t>
+        </is>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SY0901</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>2024-10-29 ---- 2024-10-22 ---- 2024-10-22 ---- 2024-02-14 ---- 2024-02-06 ---- 2024-01-26</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2024: A school held by pro-Iran militia was hit by US airstrikes as part of the Global Coalition._x000D_
+ ---- As reported in October 2024: An educational facility was occupied by the SDF military. ---- October 2024: An educational facility occupied by the SDF military was attacked by opposition forces. ---- February 2024: The SDF were stationed at a school. ---- February 2024: A college building which serves as a base for the Fatimyoun militia, was targeted by US strikes. ---- January 2024: educator executed by a firing squad belonging to an Islamic State cell. </t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Unspecified Location</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Other ---- NSA ---- NSA ---- Host Government: Military ---- Other ---- NSA</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>International Coalition Forces in Syria ---- Syrian Democratic Forces ---- Unidentified Armed Actor ---- Syrian Democratic Forces ---- International Coalition Forces in Syria ---- Islamic State</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aerial Bomb: Plane ---- No Information on the Weapon Used ---- Shelling ---- Firearms ---- Aerial Bomb: Plane ---- Firearms</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Not Applicable</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Deir ez Zor</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>SY09</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Strategic developments ---- Strategic developments ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Violence against civilians ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Abduction/forced disappearance ---- Arrests ---- Change to group/activity ---- Grenade ---- Shelling/artillery/missile attack ---- Air/drone strike ---- Abduction/forced disappearance ---- Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Military Forces of Iran (1989-) Islamic Revolutionary Guard Corps ---- Police Forces of Syria (2000-2024) ---- QSD: Syrian Democratic Forces ---- Unidentified Armed Group (Syria) ---- Tribal and Clan Forces ---- Global Coalition Against Daesh ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Military Forces of Iran (1989-) Islamic Revolutionary Guard Corps ---- Military Forces of the United States (2021-2025)</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Civilians (Syria) ---- Civilians (Syria) ---- QSD: Syrian Democratic Forces ---- Militia (Pro-Iran) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Students (Syria) ---- Students (Syria) ---- Teachers (Syria)</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>On 27 March 2024, IRGC detained three university students while they were taking photos of their building which was destroyed by airstrikes two days earlier in Deir-ez-Zor - Al-Qosor city in Deir ez Zor governorate. ---- On 31 March 2024, a Syrian police patrol, accompanied by security members from the IRGC, arrested 11 civilians, including university students, in the city of Deir-ez-Zor on allegations of photographing military positions. ---- Movement of forces: On 16 June 2024, QSD forces evacuated a military base at Al Jarsiya School in the town of Shiheil in the countryside of Deir ez Zor. ---- On 22 October 2024, an unidentified armed group targeted an educational institute in the town of Basira in the countryside of Deir ez Zor with a grenade. There were no casualties. ---- On 22 October 2024, Tribal and Clan Forces shelled a QSD military post inside a school in the village Hejneh in the countryside of Deir ez Zor with artillery, wounding two QSD members. There were no fatalities. ---- On 29 October 2024, US warplanes, operating under the Global Coalition, conducted an airstrike targeting a school held by pro-Iran militia in the village of Mathlum in the countryside of Deir ez Zor. casualties unknown. ---- On 22 January 2025, QSD forces launched a security operation and raided houses in Al Shanan, Thiban and Shiheil towns in Deir ez Zor countryside, and detained eight people including teachers and people with special needs for unknown reasons. The raids also included destroying contents of the houses and intimidation of women and children. ---- On 6 February 2025, QSD forces detained a man who works in an education institution in Maamel - 7 KM area in Deir ez Zor countryside for unknown reasons.</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>2024-03-27 ---- 2024-03-31 ---- 2024-06-16 ---- 2024-10-22 ---- 2024-10-22 ---- 2024-10-29 ---- 2025-01-22 ---- 2025-02-06</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>Deir ez Zor</t>
+        </is>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SY0902</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Deir ez Zor</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>SY09</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Violence against civilians ---- Riots ---- Battles ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Change to group/activity ---- Attack ---- Mob violence ---- Armed clash ---- Attack</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>QSD: Syrian Democratic Forces ---- Unidentified Armed Group (Syria) ---- Rioters (Syria) ---- Al Hassoun Tribal Militia (Syria) ---- Unidentified Armed Group (Syria)</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Civilians (Syria) ---- Military Forces of Syria (2000-2024) 47th Armored Brigade ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Al Mashahdeh Tribal Militia (Syria) ---- Teachers (Syria)</t>
+        </is>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>Movement of forces: On 30 January 2024, QSD forces evacuated a base that was previously a school in Abu Hamam in the countryside of Deir ez Zor. ---- On 3 October 2024, unknown gunmen shot and killed a man near a school in Kishkiyeh town in Deir ez Zor countryside over an old dispute. 1 fatality. ---- On 14 October 2024, locals stormed the educational center in the village of Sosa in the countryside of Deir ez Zor and burned the new curriculum imposed by DFNS on schools. ---- On 7 November 2024, clashes took place after regime 47th Armored Brigade members whom are from Al Mashahdeh tribe assaulted an Al Hassoun tribal member at their checkpoint in Al-Bukamal town in Deir ez Zor countryside, which resulted in clashes, injuring three Al Mashahdeh tribal members including a teacher. There were no fatalities. On 16 November 2024, an agreement, mediated by regime forces, was reached between Al Hassoun and Al Mashahdeh tribal militia members stipulating that the regime will arrest those involved in an attack in exchange for tribal militia avoiding setting up checkpoints in the city. ---- On 2 August 2025, unidentified gunmen shot and killed an elementary school principal in Shafa town in rural Deir ez Zor over an old dispute. 1 fatality.</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>2024-01-30 ---- 2024-10-03 ---- 2024-10-14 ---- 2024-11-07 ---- 2025-08-02</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>Abu Kamal</t>
+        </is>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SY0903</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2024-10-22 ---- 2024-01-18</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>October 2024: An educational facility was attacked with a grenade by an unidentified armed group. ---- January 2024: Local gunmen attacked checkpoints near a school amidst artillery shelling by Iran-backed militias.</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>NSA ---- NSA</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Actor ---- Unidentified Armed Actor</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Hand Grenade ---- Firearms</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>School: No Further Details ---- School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Deir ez Zor</t>
+        </is>
+      </c>
+      <c r="AD34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>SY09</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Violence against civilians ---- Battles ---- Explosions/Remote violence ---- Battles ---- Explosions/Remote violence ---- Battles ---- Strategic developments ---- Violence against civilians ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Attack ---- Change to group/activity ---- Change to group/activity ---- Change to group/activity ---- Change to group/activity ---- Change to group/activity ---- Attack ---- Armed clash ---- Shelling/artillery/missile attack ---- Armed clash ---- Shelling/artillery/missile attack ---- Armed clash ---- Headquarters or base established ---- Abduction/forced disappearance ---- Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>Islamic State in Iraq and the Levant (ISIL) ---- Militia (Pro-Iran) ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces ---- Military Forces of Syria (2000-2024) ---- QSD: Syrian Democratic Forces ---- Unidentified Armed Group (Syria) ---- QSD: Syrian Democratic Forces ---- Military Forces of Syria (2000-2024) ---- Fatemiyoun Brigade ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Militia (Pro-Iran)</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Civilians (Syria) ---- Civilians (Syria) ---- QSD: Syrian Democratic Forces ---- Military Forces of Syria (2000-2024) ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces ---- Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Teachers (Syria) ---- Students (Syria) ---- Civilians (Syria); Students (Syria) ---- Teachers (Syria) ---- Teachers (Syria)</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>On 26 January 2024, IS members shot and killed a teacher in Al-Hawayij town in Deir ez Zor countryside. 1 fatality. ---- Movement of forces: On 28 January 2024, pro-Iran militias evacuated their bases in In Al-Tammu neighborhood and near Al Hasan school as well as the farms in the town of Al Mayadin in the countryside of Deir ez Zor. ---- Movement of forces: On 30 January 2024, QSD forces evacuated a base that was previously a school in Abu Hardoub in the countryside of Deir ez Zor. ---- Movement of forces: On 30 January 2024, QSD forces evacuated a base that was previously a school in Eastern Jurdi in the countryside of Deir ez Zor. ---- Movement of forces: On 30 January 2024, QSD forces evacuated a base that was previously a school in Al Mawh in Thiban in the countryside of Deir ez Zor. ---- Movement of forces: On 30 January 2024, QSD forces evacuated a base that was previously a school in Al-Diaf in the countryside of Deir ez Zor. ---- On 14 February 2024, QSD members shot and killed a child in a school in Al Shanan town in Deir ez Zor countryside. 1 fatality. ---- On 24 February 2024, armed clashes took place between regime members and QSD fighters by the Euphrates river between Sweidan Jazira and Sweidan Shamiyeh in rural Deir ez Zor, causing material damage to civilian residences, a school and a water station. Casualties unknown. ---- On 28 February 2024, QSD shelled regime forces positions in Al Mayadin town in Deir ez Zor countryside with mortar shells, killing a civilian who is a high school student and injuring two others. 1 fatality. ---- On 13 April 2024, unidentified gunmen targeted a QSD-affiliated position in a school near Al Shanan village in rural eastern Deir ez Zor, triggering QSD fighters to fire gunshots randomly. Casualties unknown. ---- On 28 September 2024, QSD fighters shelled around Al Mayadin - City Bridge in rural Deir ez Zor and near a school in Al Mayadin city and its outskirts with mortars. Casualties unknown. ---- On 28 September 2024, armed clashes took place between regime members and pro-Iranian militia stationed in Al Mayadin city against QSD fighters on the opposite bank of the Euphrates river with light and medium weapons in conjunction with QSD fighters shelling near a school in Al Mayadin city in rural Deir ez Zor with mortars without causing any casualties. ---- On 29 September 2024, Fatemiyoun Brigade established a new military base in a school in the village of Quriyeh in the countryside of Deir ez Zor. ---- On 22 January 2025, QSD forces launched a security operation and raided houses in Al Shanan, Thiban and Shiheil towns in Deir ez Zor countryside, and detained eight people including teachers and people with special needs for unknown reasons. The raids also included destroying contents of the houses and intimidation of women and children. ---- On 22 January 2025, QSD forces launched a security operation and raided houses in Al Shanan, Thiban and Shiheil towns in Deir ez Zor countryside, and detained eight people including teachers and people with special needs for unknown reasons. The raids also included destroying contents of the houses and intimidation of women and children.</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>2024-01-26 ---- 2024-01-28 ---- 2024-01-30 ---- 2024-01-30 ---- 2024-01-30 ---- 2024-01-30 ---- 2024-02-14 ---- 2024-02-24 ---- 2024-02-28 ---- 2024-04-13 ---- 2024-09-28 ---- 2024-09-28 ---- 2024-09-29 ---- 2025-01-22 ---- 2025-01-22</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>Al Mayadin</t>
+        </is>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SY1000</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>September 2024: The body of a educator was found with gunshot injuries.</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Private Travel</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Tartous</t>
+        </is>
+      </c>
+      <c r="AD35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>SY10</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Protests ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Attack ---- Peaceful protest ---- Attack</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Unidentified Armed Group (Syria)</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Teachers (Syria)</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Teachers (Syria) ---- Alawite Muslim Group (Syria); Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>Around 21 September 2024 (week of), the body of a young man was found with signs of gunshot wounds along an agricultural road east of Mi'yar Shaker in rural Tartous, killed by unidentified gunmen for unknown reasons. The victim is a teacher in his 40s. 1 fatality. ---- On 27 January 2025, dozens of teachers staged a protest in the city of Tartous, opposing the caretaker government's decision to revoke their right to choose their workplace and to mandate their return to their original areas. ---- On 30 March 2025, Syrian police members shot and killed a seventeen-year-old child who is an Alawite high school student near the Karto village junction near the village of Kareemeh in the countryside of Tartous after he attempted to escape a checkpoint Syrian police members had set-up along the road. The victim is from Shass village. 1 fatality.</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>2024-09-21 ---- 2025-01-27 ---- 2025-03-30</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>Tartous</t>
+        </is>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SY1101</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>2025-02-01 ---- 2024-11-02</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">February 2025: An educational facility was hit by Turkish forces, who conducted four airstrikes on SDF positions. ---- November 2024: Five educators were arrested by the SDF after they resigned in protest against an SDF-imposed curriculum. </t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Education Building  ---- Unspecified Location</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Foreign Forces - Military ---- NSA</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Armed Forces of Turkey ---- Syrian Democratic Forces</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aerial Bomb: Plane ---- Firearms</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>University ---- Not Applicable</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>NoInformation</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ar Raqqa</t>
+        </is>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>SY11</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Strategic developments ---- Violence against civilians ---- Violence against civilians ---- Riots ---- Battles ---- Violence against civilians ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Disrupted weapons use ---- Arrests ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Violent demonstration ---- Armed clash ---- Abduction/forced disappearance ---- Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>Police Forces of Syria (2000-2024) ---- Military Forces of Syria (2000-2024) ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces ---- Rioters (Syria) ---- Unidentified Armed Group (Syria) ---- QSD: Syrian Democratic Forces ---- QSD: Syrian Democratic Forces</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- QSD: Syrian Democratic Forces ---- Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Students (Syria) ---- Teachers (Syria); Women (Syria) ---- Women (Syria); Teachers (Syria) ---- Students (Syria) ---- Teachers (Syria)</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>Defusal: On 15 July 2024, Syrian police forces dismantled an IED planted by an unidentified armed group near a polling center inside a school in the town of Maadan in the countryside of Ar Raqqa. ---- On 6 August 2024, Syrian regime forces arrested two university students at Hweijet Shnan checkpoint in the countryside of Ar Raqqa for unknown reasons. ---- On 27 October 2024, QSD forces detained four female teachers in the city of Ar-Raqqa for refusing to teach the new curriculum imposed by the group. ---- On 2 November 2024, QSD fighters detained five female teachers in Ar-Raqqa city after the teachers resigned from their positions in condemnation of a QSD-imposed teaching curricula which includes 'false historical and geographical information'. During the past few days, the teachers participated in a strike for the same reason. ---- On 2 November 2024, residents held a demonstration in the city of Ar-Raqqa - Al-Mashlab neighborhood and blocked a main road in the neighborhood with burning tires condemning QSD's detainment of five female teachers following their resignation denouncing the QSD-affiliated school curricula imposed on schools in the area. ---- On 12 February 2025, unknown gunmen attacked a QSD military point near Al Farabi school in Al Rmeleh neighborhood in Ar-Raqqa city with machine guns. Casualties unknown. ---- On 17 March 2025, QSD forces detained a university student in the city of Ar-Raqqa for raising the Syrian flag and celebrating the 14th anniversary of the Syrian revolution. ---- On 26 April 2025, QSD forces detained the head of the exam centre, the head of the educational complex, and a teacher in the village of Sabka in the countryside of Ar-Raqqa. They also seized all equipment from the centre and relocated it to the city of Ar-Raqqa for unknown reasons.</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>2024-07-15 ---- 2024-08-06 ---- 2024-10-27 ---- 2024-11-02 ---- 2024-11-02 ---- 2025-02-12 ---- 2025-03-17 ---- 2025-04-26</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>Ar Raqqa</t>
+        </is>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SY1102</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ar Raqqa</t>
+        </is>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>SY11</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>Protesters (Syria) ---- Protesters (Syria)</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>On 16 January 2025, students of Free Aleppo University staged a protest in Tell Abiad town in Ar Raqqa countryside, demanding to liberate the eastern parts of the province from QSD forces. ---- On 8 April 2025, residents held a protest in Tell Abiad in rural Ar Rawwa condemning a recent statement by Syria's minister of education regarding the possibility school examinations would not be held in the Ras al Ain and Tell Abiad areas, previously forcing students to travel through illegal crossings towards QSD-controlled areas to take their examinations.</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>2025-01-16 ---- 2025-04-08</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>Tell Abiad</t>
+        </is>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SY1200</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2024-09-22 ---- 2024-08-23</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">September 2024: An unspecified number of schools were damaged when Israeli forces shot down a suicide drone launched from Iraq by the Islamic Resistance in Iraq as it passed through Syria toward the Golan Heights. The interception occurred in the village. ---- August 2024: The body of a man who works in a school was found near a school campus, shot and killed by unidentified perpetrators. </t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Multiple ---- No Information</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Islamic Resistance in Iraq, Israeli Defence Forces ---- No Information</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aerial Bomb: Drone, Firearms ---- Firearms</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>School: No Further Details ---- School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Dara</t>
+        </is>
+      </c>
+      <c r="AD38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>SY12</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Violence against civilians ---- Explosions/Remote violence ---- Violence against civilians ---- Battles ---- Protests ---- Violence against civilians ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Remote explosive/landmine/IED ---- Remote explosive/landmine/IED ---- Attack ---- Air/drone strike ---- Abduction/forced disappearance ---- Non-state actor overtakes territory ---- Peaceful protest ---- Abduction/forced disappearance ---- Arrests</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Unidentified Armed Group (Syria) ---- Islamic Resistance in Iraq ---- Unidentified Armed Group (Syria) ---- Southern Operations Room ---- Protesters (Syria) ---- Military Forces of Israel (2022-) ---- Police Forces of Syria (2024-)</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Military Forces of Syria (2000-2024) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Labor Group (Syria); Teachers (Syria) ---- Students (Syria) ---- Farmers (Syria); Students (Syria) ---- Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>On 17 February 2024, an IED previously planted by unidentified gunmen at a fuel depot near a school and al Saraya building in Dar'a city detonated, causing material damage without causing any casualties. ---- On 8 May 2024, an IED planted by unknown gunmen exploded in Al Mahatta area in Dar'a city, killing a civilian who is a teacher and works as a taxi driver. 1 fatality. ---- Around 23 August 2024 (week of), the body of a man who works in a school was found near Al Manar school on Abtaa-Sheikh Miskine road in Dara countryside, shot and killed by unknown gunmen. 1 fatality. ---- Interception: On 22 September 2024, Israeli forces shot down a suicide drone launched from Iraq by the Islamic Resistance in Iraq as it passed through Syria toward the Golan Heights. The interception occurred in Jomleh village in the Dara countryside, causing material damage to local schools and resulting in minor injuries to a woman from shattered glass. ---- On 19 November 2024, an unidentified armed group kidnapped a university student on the road to Abtaa in the countryside of Dara for unknown reasons. The student had previously been blackmailed for money. ---- On 6 December 2024, opposition factions operating under the Southern Operations Room clashed with regime fighters on the outskirts of Da'el and took control of a school and a checkpoint along the Da'el - Atman road and several checkpoints between Da'el and Tafas in rural Dara in conjunction with Syrian regime fighters shelling Da'el city with artillery, killing two young men during clashes along the Da'el - Tafas road and capturing two regime fighters. 2 fatalities. ---- On 25 February 2025, students from Nafeaa in rural Dara held a protest condemning a recent Israeli statement calling for the disarmament of southern Syria and condemning projects that threaten Syria's unity. ---- On 28 March 2025, Israeli forces detained three people two of whom are university students while working in a farmland in Yarmouk Basin in Dara countryside. ---- On 8 August 2025, police forces arrested a university student from As Sweida province at Busra Esh-Sham checkpoint in Dara countryside for unknown reasons.</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>2024-02-17 ---- 2024-05-08 ---- 2024-08-23 ---- 2024-09-22 ---- 2024-11-19 ---- 2024-12-06 ---- 2025-02-25 ---- 2025-03-28 ---- 2025-08-08</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>Dara</t>
+        </is>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SY1202</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Dara</t>
+        </is>
+      </c>
+      <c r="AD39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>SY12</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Attack ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Syria) ---- Protesters (Syria)</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Teachers (Syria)</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>Around 19 May 2024 (week of), the bodies of two individuals were found near a school in As-Sanamayn in rural northern Dara, killed by unidentified gunmen. The victims were accused of being involved in killing regime opponents. 2 fatalities. ---- On 10 February 2025, teachers staged a protest at a school in the village of Ghabagheb in the countryside of Dara, denouncing the detention of the school principal for two hours by a commander of a local armed group following a dispute between them.</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>2024-05-19 ---- 2025-02-10</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>As Sanamayn</t>
+        </is>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SY1203</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">September 2024: A school was damaged when an unidentified armed group detonated a grenade nearby._x000D_
+</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Actor</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Hand Grenade</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Dara</t>
+        </is>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>SY12</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Grenade</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Syria)</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>On 8 September 2024, an unidentified armed group detonated a grenade near a school in the town of Jasim in the countryside of Dara, causing only material damages. There were no casualties.</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>Izra</t>
+        </is>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SY1300</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>As Sweida</t>
+        </is>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>SY13</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Strategic developments ---- Protests ---- Strategic developments ---- Protests ---- Protests ---- Protests ---- Violence against civilians ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Riots ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Other ---- Change to group/activity ---- Peaceful protest ---- Arrests ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Abduction/forced disappearance ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Violent demonstration ---- Attack</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Jabal Al Arab Militia (Syria) ---- Military Forces of Syria (2000-2024) ---- Protesters (Syria) ---- Military Forces of Syria (2000-2024) Air Force Intelligence Directorate ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Unidentified Armed Group (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Protesters (Syria) ---- Rioters (Syria) ---- Unidentified Armed Group (Syria)</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>As-Sweida Communal Militia (Syria) ---- Students (Syria) ---- Students (Syria) ---- Teachers (Syria) ---- Teachers (Syria) ---- Teachers (Syria) ---- Teachers (Syria) ---- Teachers (Syria)</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Military Forces of Syria (2000-2024) ---- Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Police Forces of Syria (2000-2024) State Security ---- Students (Syria); Unidentified Tribal Group (Syria) ---- Teachers (Syria) ---- Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>Other: On 25 April 2024, Jabal Al Arab Militia detained several regime officers, including the head of the local Passports &amp; Immigration branch in As-Sweida city in retaliation to the ongoing detention of a university student. On April 29, 2024, as part of a swap agreement between both parties, the officers and the university student were released. ---- Movement of forces: On 27 April 2024, for the third consecutive day, regime reinforcements including buses carrying dozens of fighters equipped with machine guns arrived in As-Sweida city from Damascus following the regime's continued detainment of a university student triggered protests. ---- On 27 April 2024, tens of residents held a protest in As-Sweida city calling for the release of detainees, the implementation of UN resolution 2254 and fall of the regime. Attendees also condemned the regime's continued detainment of a university student on charges of undermining the state. ---- On 5 October 2024, regime-affiliated Air Force Intelligence members arrested seven individuals in a hospital in As-Sweida city while searching for a person accused of drug trafficking and smuggling. All of the victims are unidentified tribal group members and include one student. ---- On 10 December 2024, students staged a protest at the Faculty of Fine Arts in the city of As-Sweida celebrating the topple of the Syrian regime. ---- On 19 December 2024, university students staged a protest in Al Karamah square in As-Sweida city, against high transportation fees that prevent them from reaching their universities in the rest of the governorates. ---- On 5 January 2025, residents including teachers held a protest in As-Sweida city calling for the development of the educational curriculum to suit the requirements of the modern era. ---- On 21 January 2025, unidentified gunmen abducted a teacher from a computer technology institute in As-Sweida city for unknown reasons. The incident took place after the teacher expelled a student who is accused of cheating. The victim's whereabouts remain unknown. ---- On 22 January 2025, locals including teachers staged a protest in front of the education directorate building in As-Sweida city, condemning violence within educational institutions and demanding accountability of the aggressors. ---- On 23 January 2025, teachers staged a protest in front of the education directorate building in As-Sweida city, against the decision of ending the duty location and returning them to their areas of origin. ---- On 24 January 2025, locals, activists and teachers staged a protest in Al Karameh square in As-Sweida city, to express their rejection of weapons and violence, and to condemn the attacks that targeted teachers recently. ---- On 9 February 2025, dozens of teachers and activists staged a protest in the city of As-Sweida against the appointment of several school principals by the Directorate of Education, who are accused of corruption. ---- On 15 February 2025, locals staged a protest in As-Sweida city, demanding the revelation of the whereabouts of a student who was kidnapped. ---- On 20 February 2025, locals staged a demonstration at the northern entrance of As-Sweida city, partially blocking the road with burning tires, demanding action to reveal the fate of university student Carolis Nahla, after she went missing on 4th of February. ---- On 31 March 2025, two unidentified gunmen on a motorcycle shot and injured a 23-year-old engineering student at the University of Aleppo and resident of As-Sweida, near Al-Ankoud roundabout in As-Sweida city. 1 injured.</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>2024-04-25 ---- 2024-04-27 ---- 2024-04-27 ---- 2024-10-05 ---- 2024-12-10 ---- 2024-12-19 ---- 2025-01-05 ---- 2025-01-21 ---- 2025-01-22 ---- 2025-01-23 ---- 2025-01-24 ---- 2025-02-09 ---- 2025-02-15 ---- 2025-02-20 ---- 2025-03-31</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>As Sweida</t>
+        </is>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SY1303</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>As Sweida</t>
+        </is>
+      </c>
+      <c r="AD42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>SY13</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Syria)</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>Civilians (Syria)</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Students (Syria)</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>Around 5 July 2025 (between 2 - 5 July), the body of a university student was found near the village of Nemreh in the countryside of As Sweida killed by an unidentified armed group, after the student had gone missing on 2 July. 1 fatality.</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>Shahba</t>
+        </is>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SY1400</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>April 2025: An education facility was raided by Israeli military forces during school hours.</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Foreign Forces - Military</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Israeli Defence Forces</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Quneitra</t>
+        </is>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>SY14</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Violence against civilians ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Abduction/forced disappearance ---- Looting/property destruction ---- Change to group/activity ---- Change to group/activity ---- Abduction/forced disappearance ---- Looting/property destruction</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-)</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr">
+        <is>
           <t>Civilians (Syria) ---- Civilians (Syria) ---- Civilians (Syria) ---- Government of Syria (2024-)</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AM43" t="inlineStr">
         <is>
           <t>Students (Syria)</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
+      <c r="AN43" t="inlineStr">
         <is>
           <t>On 8 December 2024, Israeli fighters detained all residents of Rasm al Rawadi village in rural Quneitra as part of a combing operation. They kept them in a school in the village, causing resentment among the victims. Following this, Israeli fighters withdrew from the village. ---- Property destruction: On 5 January 2025, Israeli fighters entered Kodneh village in rural Quneitra and erected barriers to cut off a road leading to a forested area where they bulldozed the forested area, leading to the closure of local schools in the village. Local residents attempted to prevent Israeli fighters from advancing. ---- Movement of forces: On 4 April 2025, Israeli forces advanced inside Rweheineh town in Quneitra countryside, and set up a checkpoint near a school. ---- Movement of forces: On 22 April 2025, an Israeli patrol including seven military vehicles entered Al Qahtaniyah town in rural Quneitra and conducted searches of residential homes and a school and its surroundings (during school hours) in the town in search of weapons, causing panic among civilians. ---- On 14 June 2025, Israeli forces stormed a school in the village of Kodneh in Quneitra countryside, detained two children, and fired warning shots in the air, alleging they were taking pictures of Israeli military posts. ---- Property destruction: On 15 June 2025, Israeli forces stormed a public school in the village of Hurriyeh in the Quneitra countryside and vandalized its furniture.</t>
         </is>
       </c>
-      <c r="AO21" t="inlineStr">
+      <c r="AO43" t="inlineStr">
         <is>
           <t>2024-12-08 ---- 2025-01-05 ---- 2025-04-04 ---- 2025-04-22 ---- 2025-06-14 ---- 2025-06-15</t>
         </is>
       </c>
-      <c r="AP21" t="inlineStr">
+      <c r="AP43" t="inlineStr">
         <is>
           <t>Quneitra</t>
         </is>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AQ43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4074,13 +6164,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B9FE85B-9DDC-44F5-B240-345898B035DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1326C54-1AF4-43E8-8613-28067D7E22A9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92AE698B-A72C-40C6-9BE4-6B23447615F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE356261-DEF7-4A51-A7E3-BF352E96F419}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFDBBB62-E07B-4F4B-8409-8C82443242D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3C8714-80EB-421C-BAC7-7A91F66B7DCF}"/>
 </file>